--- a/final_deliverables/v5/効果試算_v5.xlsx
+++ b/final_deliverables/v5/効果試算_v5.xlsx
@@ -20,14 +20,15 @@
     <definedName name="sales_total">'入力'!$C$6</definedName>
     <definedName name="n_all">'入力'!$C$7</definedName>
     <definedName name="n_resp">'入力'!$C$8</definedName>
-    <definedName name="rx_resp">'入力'!$C$9</definedName>
-    <definedName name="mkt_share">'入力'!$C$10</definedName>
-    <definedName name="sales_per_pt">'入力'!$C$11</definedName>
-    <definedName name="conv_low">'入力'!$C$12</definedName>
-    <definedName name="conv_base">'入力'!$C$13</definedName>
-    <definedName name="conv_high">'入力'!$C$14</definedName>
-    <definedName name="prod_cost">'入力'!$C$15</definedName>
-    <definedName name="ops_cost">'入力'!$C$16</definedName>
+    <definedName name="n_market">'入力'!$C$9</definedName>
+    <definedName name="scale">'入力'!$C$10</definedName>
+    <definedName name="rx_resp">'入力'!$C$11</definedName>
+    <definedName name="sales_per_pt">'入力'!$C$12</definedName>
+    <definedName name="conv_low">'入力'!$C$13</definedName>
+    <definedName name="conv_base">'入力'!$C$14</definedName>
+    <definedName name="conv_high">'入力'!$C$15</definedName>
+    <definedName name="prod_cost">'入力'!$C$16</definedName>
+    <definedName name="ops_cost">'入力'!$C$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -36,10 +37,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0"/>
-    <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -90,12 +91,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DCE6F5"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00DCE6F5"/>
       </patternFill>
     </fill>
     <fill>
@@ -130,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -142,27 +143,28 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -531,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -660,7 +662,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>全医師数</t>
+          <t>データの医師数</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
@@ -678,7 +680,7 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>データ仕様書: doctor_attributes「全10,000名」</t>
+          <t>データ仕様書: doctor_attributes 10,000名(市場全体の一部として扱う)</t>
         </is>
       </c>
     </row>
@@ -715,30 +717,30 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>実測</t>
+          <t>資料</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>回答医師の薬剤A処方患者数</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="n">
-        <v>11280</v>
+          <t>市場全体の医師数(m3.com登録医師)</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>310000</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>人</t>
+          <t>名</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>rx_resp</t>
+          <t>n_market</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>survey_2026 Q3_2の合計(直近1年・自己申告)</t>
+          <t>M3会社資料: 国内医師の約90%(31万人以上)がm3.comに登録</t>
         </is>
       </c>
     </row>
@@ -750,52 +752,56 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>全医師10,000名の処方が売上50億円に占める割合</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="4" t="inlineStr"/>
+          <t>全国換算の倍率</t>
+        </is>
+      </c>
+      <c r="C10" s="7">
+        <f>n_market/n_resp</f>
+        <v/>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>倍</t>
+        </is>
+      </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>mkt_share</t>
+          <t>scale</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>仮定(要確認)。データ仕様書で10,000名が「全医師」のため100%</t>
+          <t>回答医師5,000名が市場全体と同じ構成と仮定(非回答医師とも診療科・MR面談・配信の構成はほぼ同じ)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>仮定</t>
+          <t>実測</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>処方患者1人あたり年間売上</t>
-        </is>
-      </c>
-      <c r="C11" s="9">
-        <f>sales_total*mkt_share/(rx_resp*n_all/n_resp)</f>
-        <v/>
+          <t>回答医師の薬剤A処方患者数</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="n">
+        <v>11280</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>円</t>
+          <t>人</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>sales_per_pt</t>
+          <t>rx_resp</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>初期値=50億円×割合÷全医師の処方患者推計(回答医師×2)。実際の単価が分かれば数値で上書き</t>
+          <t>survey_2026 Q3_2の合計(直近1年・自己申告)</t>
         </is>
       </c>
     </row>
@@ -807,21 +813,26 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>増分転換率_保守</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D12" s="4" t="inlineStr"/>
+          <t>処方患者1人あたり年間売上</t>
+        </is>
+      </c>
+      <c r="C12" s="9">
+        <f>sales_total/(rx_resp*scale)</f>
+        <v/>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>円</t>
+        </is>
+      </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>conv_low</t>
+          <t>sales_per_pt</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>既読した医師の潜在未処方のうち、配信によって新たに処方される割合。配信を減らす群で失う効果にも同じ値を使う。⑦参照</t>
+          <t>50億円 ÷ 全国の処方患者推計(回答医師の処方患者 × 倍率)。実際の単価が分かれば数値で上書き</t>
         </is>
       </c>
     </row>
@@ -833,21 +844,21 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>増分転換率_基準</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="n">
-        <v>0.03</v>
+          <t>増分転換率_保守</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="n">
+        <v>0.01</v>
       </c>
       <c r="D13" s="4" t="inlineStr"/>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>conv_base</t>
+          <t>conv_low</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>参考値(配信対象と対象外の差から換算)の95%区間の下限2.8%に相当</t>
+          <t>既読した医師の潜在未処方のうち、配信によって新たに処方される割合。配信を減らす群で失う効果にも同じ値を使う。⑦参照</t>
         </is>
       </c>
     </row>
@@ -859,51 +870,47 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>増分転換率_楽観</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="n">
-        <v>0.06</v>
+          <t>増分転換率_基準</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="n">
+        <v>0.03</v>
       </c>
       <c r="D14" s="4" t="inlineStr"/>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>conv_high</t>
+          <t>conv_base</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>参考値の中央6.0%に相当(観察された差をすべて配信の効果とみなす)</t>
+          <t>参考値(配信対象と対象外の差から換算)の95%区間の下限2.8%に相当</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>仮定</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>コンテンツ制作費(年)</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>円</t>
-        </is>
-      </c>
+          <t>増分転換率_楽観</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="D15" s="4" t="inlineStr"/>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>prod_cost</t>
+          <t>conv_high</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>既存10本の並べ替え・再配信のみの前提で0。新規制作する場合は入力</t>
+          <t>参考値の中央6.0%に相当(観察された差をすべて配信の効果とみなす)</t>
         </is>
       </c>
     </row>
@@ -915,7 +922,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>配信設定・運用管理費(年)</t>
+          <t>コンテンツ制作費(年)</t>
         </is>
       </c>
       <c r="C16" s="9" t="n">
@@ -928,283 +935,313 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
+          <t>prod_cost</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>既存10本の並べ替え・再配信のみの前提で0。新規制作する場合は入力</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>配信設定・運用管理費(年)</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>円</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
           <t>ops_cost</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t>未確認。判明したら入力(A案・B案の費用に加算)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>群別の入力(医師ごとに主要施策を1つ。群は重複しない)</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>群</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>医師数</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>潜在未処方(人)</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>1配信あたり既読率</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>年10回配信時の既読医師率</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>現状の年間配信回数</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>A案の年間配信回数</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>B案の年間配信回数</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr">
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>翌年比(平均への回帰)</t>
         </is>
       </c>
-      <c r="J19" s="3" t="inlineStr">
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>出典・根拠</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>① 未接触・潜在8人以上(重点医師)</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="n">
-        <v>191</v>
-      </c>
-      <c r="C20" s="10" t="n">
-        <v>2042</v>
-      </c>
-      <c r="D20" s="11" t="n">
-        <v>0.09693877551020408</v>
-      </c>
-      <c r="E20" s="12" t="n">
-        <v>0.4872448979591837</v>
-      </c>
-      <c r="F20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="14" t="n">
-        <v>12</v>
-      </c>
-      <c r="H20" s="14" t="n">
-        <v>12</v>
-      </c>
-      <c r="I20" s="15" t="n">
-        <v>0.7755905511811023</v>
-      </c>
-      <c r="J20" s="6" t="inlineStr">
-        <is>
-          <t>内科・耳鼻で潜在8人以上、MR面談なし・MR君未配信。既読率は配信中・MR面談なしの重点医師(②)の実測値を使う(仮定)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>② 配信中・潜在8人以上(重点医師)</t>
-        </is>
-      </c>
-      <c r="B21" s="10" t="n">
-        <v>392</v>
-      </c>
-      <c r="C21" s="10" t="n">
-        <v>4005</v>
-      </c>
-      <c r="D21" s="11" t="n">
+          <t>① 未接触・潜在8人以上(重点医師)</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="n">
+        <v>191</v>
+      </c>
+      <c r="C21" s="11" t="n">
+        <v>2042</v>
+      </c>
+      <c r="D21" s="12" t="n">
         <v>0.09693877551020408</v>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="E21" s="13" t="n">
         <v>0.4872448979591837</v>
       </c>
-      <c r="F21" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="G21" s="14" t="n">
+      <c r="F21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="H21" s="14" t="n">
+      <c r="H21" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="I21" s="15" t="n">
+      <c r="I21" s="16" t="n">
         <v>0.7755905511811023</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>内科・耳鼻で潜在8人以上、MR面談なし・MR君配信中。既読率は実測</t>
+          <t>内科・耳鼻で潜在8人以上、MR面談なし・MR君未配信。既読率は配信中・MR面談なしの重点医師(②)の実測値を使う(仮定)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>③ 配信中・潜在0〜2人(財源)</t>
-        </is>
-      </c>
-      <c r="B22" s="10" t="n">
-        <v>993</v>
-      </c>
-      <c r="C22" s="10" t="n">
-        <v>1511</v>
-      </c>
-      <c r="D22" s="11" t="n">
-        <v>0.1173212487411883</v>
-      </c>
-      <c r="E22" s="12" t="n">
-        <v>0.5115810674723061</v>
-      </c>
-      <c r="F22" s="13" t="n">
+          <t>② 配信中・潜在8人以上(重点医師)</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="n">
+        <v>392</v>
+      </c>
+      <c r="C22" s="11" t="n">
+        <v>4005</v>
+      </c>
+      <c r="D22" s="12" t="n">
+        <v>0.09693877551020408</v>
+      </c>
+      <c r="E22" s="13" t="n">
+        <v>0.4872448979591837</v>
+      </c>
+      <c r="F22" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="G22" s="14" t="n">
-        <v>6</v>
-      </c>
-      <c r="H22" s="14" t="n">
-        <v>6</v>
-      </c>
-      <c r="I22" s="15" t="n">
-        <v>2.160606060606061</v>
+      <c r="G22" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="H22" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="I22" s="16" t="n">
+        <v>0.7755905511811023</v>
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>A案の財源。全診療科で潜在0〜2人の配信対象。翌年比は全診療科・潜在0〜2人の実測値(平均への回帰で翌年は増える)</t>
+          <t>内科・耳鼻で潜在8人以上、MR面談なし・MR君配信中。既読率は実測</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>④ MR面談あり・潜在8人以上(重点医師、配信中)</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="n">
-        <v>82</v>
-      </c>
-      <c r="C23" s="10" t="n">
-        <v>787</v>
-      </c>
-      <c r="D23" s="11" t="n">
-        <v>0.09146341463414634</v>
-      </c>
-      <c r="E23" s="12" t="n">
-        <v>0.3902439024390244</v>
-      </c>
-      <c r="F23" s="13" t="n">
+          <t>③ 配信中・潜在0〜2人(財源)</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="n">
+        <v>993</v>
+      </c>
+      <c r="C23" s="11" t="n">
+        <v>1511</v>
+      </c>
+      <c r="D23" s="12" t="n">
+        <v>0.1173212487411883</v>
+      </c>
+      <c r="E23" s="13" t="n">
+        <v>0.5115810674723061</v>
+      </c>
+      <c r="F23" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="G23" s="14" t="n">
-        <v>10</v>
-      </c>
-      <c r="H23" s="14" t="n">
-        <v>10</v>
-      </c>
-      <c r="I23" s="15" t="n">
-        <v>0.7755905511811023</v>
+      <c r="G23" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="H23" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="I23" s="16" t="n">
+        <v>2.160606060606061</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>重点医師のうちMR面談あり(118名)で配信中の82名。現状維持</t>
+          <t>A案の財源。全診療科で潜在0〜2人の配信対象。翌年比は全診療科・潜在0〜2人の実測値(平均への回帰で翌年は増える)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>⑤ 未接触・潜在5〜7人(B案で追加)</t>
-        </is>
-      </c>
-      <c r="B24" s="10" t="n">
-        <v>260</v>
-      </c>
-      <c r="C24" s="10" t="n">
-        <v>1546</v>
-      </c>
-      <c r="D24" s="11" t="n">
-        <v>0.1191616766467066</v>
-      </c>
-      <c r="E24" s="12" t="n">
-        <v>0.5229540918163673</v>
-      </c>
-      <c r="F24" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="14" t="n">
-        <v>12</v>
-      </c>
-      <c r="I24" s="15" t="n">
-        <v>1.017937219730942</v>
+          <t>④ MR面談あり・潜在8人以上(重点医師、配信中)</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="n">
+        <v>82</v>
+      </c>
+      <c r="C24" s="11" t="n">
+        <v>787</v>
+      </c>
+      <c r="D24" s="12" t="n">
+        <v>0.09146341463414634</v>
+      </c>
+      <c r="E24" s="13" t="n">
+        <v>0.3902439024390244</v>
+      </c>
+      <c r="F24" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G24" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="H24" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="I24" s="16" t="n">
+        <v>0.7755905511811023</v>
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>B案で追加。既読率は同じ条件(内科・耳鼻・面談なし・潜在5〜7人)で配信中の医師の実測値</t>
+          <t>重点医師のうちMR面談あり(118名)で配信中の82名。現状維持</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
+          <t>⑤ 未接触・潜在5〜7人(B案で追加)</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="n">
+        <v>260</v>
+      </c>
+      <c r="C25" s="11" t="n">
+        <v>1546</v>
+      </c>
+      <c r="D25" s="12" t="n">
+        <v>0.1191616766467066</v>
+      </c>
+      <c r="E25" s="13" t="n">
+        <v>0.5229540918163673</v>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="I25" s="16" t="n">
+        <v>1.017937219730942</v>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>B案で追加。既読率は同じ条件(内科・耳鼻・面談なし・潜在5〜7人)で配信中の医師の実測値</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
           <t>その他の配信中(変更なし)</t>
         </is>
       </c>
-      <c r="B25" s="10" t="n">
+      <c r="B26" s="11" t="n">
         <v>2014</v>
       </c>
-      <c r="C25" s="10" t="n">
+      <c r="C26" s="11" t="n">
         <v>9421</v>
       </c>
-      <c r="D25" s="11" t="n">
+      <c r="D26" s="12" t="n">
         <v>0.1183714001986097</v>
       </c>
-      <c r="E25" s="12" t="inlineStr"/>
-      <c r="F25" s="13" t="n">
+      <c r="E26" s="13" t="inlineStr"/>
+      <c r="F26" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="G25" s="14" t="n">
+      <c r="G26" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="H25" s="14" t="n">
+      <c r="H26" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="I25" s="15" t="n">
+      <c r="I26" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="J25" s="6" t="inlineStr">
+      <c r="J26" s="6" t="inlineStr">
         <is>
           <t>上記以外の配信対象。既読率は残りの既読件数から逆算</t>
         </is>
@@ -1321,12 +1358,12 @@
 (内科89・耳鼻102)</t>
         </is>
       </c>
-      <c r="B5" s="16">
-        <f>'入力'!$B$20</f>
-        <v/>
-      </c>
-      <c r="C5" s="16">
-        <f>'入力'!$C$20</f>
+      <c r="B5" s="17">
+        <f>'入力'!$B$21</f>
+        <v/>
+      </c>
+      <c r="C5" s="17">
+        <f>'入力'!$C$21</f>
         <v/>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -1345,14 +1382,14 @@
         </is>
       </c>
       <c r="G5" s="6">
-        <f>'入力'!$G$20</f>
-        <v/>
-      </c>
-      <c r="H5" s="16">
+        <f>'入力'!$G$21</f>
+        <v/>
+      </c>
+      <c r="H5" s="17">
         <f>'④費用計算'!E6</f>
         <v/>
       </c>
-      <c r="I5" s="16">
+      <c r="I5" s="17">
         <f>'④費用計算'!H6</f>
         <v/>
       </c>
@@ -1379,12 +1416,12 @@
 (内科162・耳鼻230)</t>
         </is>
       </c>
-      <c r="B6" s="16">
-        <f>'入力'!$B$21</f>
-        <v/>
-      </c>
-      <c r="C6" s="16">
-        <f>'入力'!$C$21</f>
+      <c r="B6" s="17">
+        <f>'入力'!$B$22</f>
+        <v/>
+      </c>
+      <c r="C6" s="17">
+        <f>'入力'!$C$22</f>
         <v/>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -1403,14 +1440,14 @@
         </is>
       </c>
       <c r="G6" s="6">
-        <f>'入力'!$G$21</f>
-        <v/>
-      </c>
-      <c r="H6" s="16">
+        <f>'入力'!$G$22</f>
+        <v/>
+      </c>
+      <c r="H6" s="17">
         <f>'④費用計算'!E7</f>
         <v/>
       </c>
-      <c r="I6" s="16">
+      <c r="I6" s="17">
         <f>'④費用計算'!H7</f>
         <v/>
       </c>
@@ -1437,12 +1474,12 @@
 (内科343・耳鼻67・小児390・眼科193)</t>
         </is>
       </c>
-      <c r="B7" s="16">
-        <f>'入力'!$B$22</f>
-        <v/>
-      </c>
-      <c r="C7" s="16">
-        <f>'入力'!$C$22</f>
+      <c r="B7" s="17">
+        <f>'入力'!$B$23</f>
+        <v/>
+      </c>
+      <c r="C7" s="17">
+        <f>'入力'!$C$23</f>
         <v/>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -1461,14 +1498,14 @@
         </is>
       </c>
       <c r="G7" s="6">
-        <f>'入力'!$G$22</f>
-        <v/>
-      </c>
-      <c r="H7" s="16">
+        <f>'入力'!$G$23</f>
+        <v/>
+      </c>
+      <c r="H7" s="17">
         <f>'④費用計算'!E8</f>
         <v/>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="17">
         <f>'④費用計算'!H8</f>
         <v/>
       </c>
@@ -1495,12 +1532,12 @@
 (内科31・耳鼻51)</t>
         </is>
       </c>
-      <c r="B8" s="16">
-        <f>'入力'!$B$23</f>
-        <v/>
-      </c>
-      <c r="C8" s="16">
-        <f>'入力'!$C$23</f>
+      <c r="B8" s="17">
+        <f>'入力'!$B$24</f>
+        <v/>
+      </c>
+      <c r="C8" s="17">
+        <f>'入力'!$C$24</f>
         <v/>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -1519,14 +1556,14 @@
         </is>
       </c>
       <c r="G8" s="6">
-        <f>'入力'!$G$23</f>
-        <v/>
-      </c>
-      <c r="H8" s="16">
+        <f>'入力'!$G$24</f>
+        <v/>
+      </c>
+      <c r="H8" s="17">
         <f>'④費用計算'!E9</f>
         <v/>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="17">
         <f>'④費用計算'!H9</f>
         <v/>
       </c>
@@ -1553,12 +1590,12 @@
 (内科162・耳鼻98)</t>
         </is>
       </c>
-      <c r="B9" s="16">
-        <f>'入力'!$B$24</f>
-        <v/>
-      </c>
-      <c r="C9" s="16">
-        <f>'入力'!$C$24</f>
+      <c r="B9" s="17">
+        <f>'入力'!$B$25</f>
+        <v/>
+      </c>
+      <c r="C9" s="17">
+        <f>'入力'!$C$25</f>
         <v/>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -1577,14 +1614,14 @@
         </is>
       </c>
       <c r="G9" s="6">
-        <f>'入力'!$H$24</f>
-        <v/>
-      </c>
-      <c r="H9" s="16">
+        <f>'入力'!$H$25</f>
+        <v/>
+      </c>
+      <c r="H9" s="17">
         <f>'④費用計算'!F10</f>
         <v/>
       </c>
-      <c r="I9" s="16">
+      <c r="I9" s="17">
         <f>'④費用計算'!I10</f>
         <v/>
       </c>
@@ -2060,39 +2097,39 @@
         </is>
       </c>
       <c r="B5" s="4">
-        <f>'入力'!$F$20</f>
+        <f>'入力'!$F$21</f>
         <v/>
       </c>
       <c r="C5" s="4">
-        <f>'入力'!$G$20</f>
+        <f>'入力'!$G$21</f>
         <v/>
       </c>
       <c r="D5" s="4">
-        <f>'入力'!$H$20</f>
-        <v/>
-      </c>
-      <c r="E5" s="17">
-        <f>IF('入力'!$F$20&gt;0,'入力'!$B$20,0)</f>
-        <v/>
-      </c>
-      <c r="F5" s="17">
-        <f>IF('入力'!$G$20&gt;0,'入力'!$B$20,0)</f>
-        <v/>
-      </c>
-      <c r="G5" s="17">
-        <f>IF('入力'!$H$20&gt;0,'入力'!$B$20,0)</f>
-        <v/>
-      </c>
-      <c r="H5" s="17">
-        <f>'入力'!$B$20*'入力'!$F$20</f>
-        <v/>
-      </c>
-      <c r="I5" s="17">
-        <f>'入力'!$B$20*'入力'!$G$20</f>
-        <v/>
-      </c>
-      <c r="J5" s="17">
-        <f>'入力'!$B$20*'入力'!$H$20</f>
+        <f>'入力'!$H$21</f>
+        <v/>
+      </c>
+      <c r="E5" s="18">
+        <f>IF('入力'!$F$21&gt;0,'入力'!$B$21,0)</f>
+        <v/>
+      </c>
+      <c r="F5" s="18">
+        <f>IF('入力'!$G$21&gt;0,'入力'!$B$21,0)</f>
+        <v/>
+      </c>
+      <c r="G5" s="18">
+        <f>IF('入力'!$H$21&gt;0,'入力'!$B$21,0)</f>
+        <v/>
+      </c>
+      <c r="H5" s="18">
+        <f>'入力'!$B$21*'入力'!$F$21</f>
+        <v/>
+      </c>
+      <c r="I5" s="18">
+        <f>'入力'!$B$21*'入力'!$G$21</f>
+        <v/>
+      </c>
+      <c r="J5" s="18">
+        <f>'入力'!$B$21*'入力'!$H$21</f>
         <v/>
       </c>
     </row>
@@ -2103,39 +2140,39 @@
         </is>
       </c>
       <c r="B6" s="4">
-        <f>'入力'!$F$21</f>
+        <f>'入力'!$F$22</f>
         <v/>
       </c>
       <c r="C6" s="4">
-        <f>'入力'!$G$21</f>
+        <f>'入力'!$G$22</f>
         <v/>
       </c>
       <c r="D6" s="4">
-        <f>'入力'!$H$21</f>
-        <v/>
-      </c>
-      <c r="E6" s="17">
-        <f>IF('入力'!$F$21&gt;0,'入力'!$B$21,0)</f>
-        <v/>
-      </c>
-      <c r="F6" s="17">
-        <f>IF('入力'!$G$21&gt;0,'入力'!$B$21,0)</f>
-        <v/>
-      </c>
-      <c r="G6" s="17">
-        <f>IF('入力'!$H$21&gt;0,'入力'!$B$21,0)</f>
-        <v/>
-      </c>
-      <c r="H6" s="17">
-        <f>'入力'!$B$21*'入力'!$F$21</f>
-        <v/>
-      </c>
-      <c r="I6" s="17">
-        <f>'入力'!$B$21*'入力'!$G$21</f>
-        <v/>
-      </c>
-      <c r="J6" s="17">
-        <f>'入力'!$B$21*'入力'!$H$21</f>
+        <f>'入力'!$H$22</f>
+        <v/>
+      </c>
+      <c r="E6" s="18">
+        <f>IF('入力'!$F$22&gt;0,'入力'!$B$22,0)</f>
+        <v/>
+      </c>
+      <c r="F6" s="18">
+        <f>IF('入力'!$G$22&gt;0,'入力'!$B$22,0)</f>
+        <v/>
+      </c>
+      <c r="G6" s="18">
+        <f>IF('入力'!$H$22&gt;0,'入力'!$B$22,0)</f>
+        <v/>
+      </c>
+      <c r="H6" s="18">
+        <f>'入力'!$B$22*'入力'!$F$22</f>
+        <v/>
+      </c>
+      <c r="I6" s="18">
+        <f>'入力'!$B$22*'入力'!$G$22</f>
+        <v/>
+      </c>
+      <c r="J6" s="18">
+        <f>'入力'!$B$22*'入力'!$H$22</f>
         <v/>
       </c>
     </row>
@@ -2146,39 +2183,39 @@
         </is>
       </c>
       <c r="B7" s="4">
-        <f>'入力'!$F$22</f>
+        <f>'入力'!$F$23</f>
         <v/>
       </c>
       <c r="C7" s="4">
-        <f>'入力'!$G$22</f>
+        <f>'入力'!$G$23</f>
         <v/>
       </c>
       <c r="D7" s="4">
-        <f>'入力'!$H$22</f>
-        <v/>
-      </c>
-      <c r="E7" s="17">
-        <f>IF('入力'!$F$22&gt;0,'入力'!$B$22,0)</f>
-        <v/>
-      </c>
-      <c r="F7" s="17">
-        <f>IF('入力'!$G$22&gt;0,'入力'!$B$22,0)</f>
-        <v/>
-      </c>
-      <c r="G7" s="17">
-        <f>IF('入力'!$H$22&gt;0,'入力'!$B$22,0)</f>
-        <v/>
-      </c>
-      <c r="H7" s="17">
-        <f>'入力'!$B$22*'入力'!$F$22</f>
-        <v/>
-      </c>
-      <c r="I7" s="17">
-        <f>'入力'!$B$22*'入力'!$G$22</f>
-        <v/>
-      </c>
-      <c r="J7" s="17">
-        <f>'入力'!$B$22*'入力'!$H$22</f>
+        <f>'入力'!$H$23</f>
+        <v/>
+      </c>
+      <c r="E7" s="18">
+        <f>IF('入力'!$F$23&gt;0,'入力'!$B$23,0)</f>
+        <v/>
+      </c>
+      <c r="F7" s="18">
+        <f>IF('入力'!$G$23&gt;0,'入力'!$B$23,0)</f>
+        <v/>
+      </c>
+      <c r="G7" s="18">
+        <f>IF('入力'!$H$23&gt;0,'入力'!$B$23,0)</f>
+        <v/>
+      </c>
+      <c r="H7" s="18">
+        <f>'入力'!$B$23*'入力'!$F$23</f>
+        <v/>
+      </c>
+      <c r="I7" s="18">
+        <f>'入力'!$B$23*'入力'!$G$23</f>
+        <v/>
+      </c>
+      <c r="J7" s="18">
+        <f>'入力'!$B$23*'入力'!$H$23</f>
         <v/>
       </c>
     </row>
@@ -2189,39 +2226,39 @@
         </is>
       </c>
       <c r="B8" s="4">
-        <f>'入力'!$F$23</f>
+        <f>'入力'!$F$24</f>
         <v/>
       </c>
       <c r="C8" s="4">
-        <f>'入力'!$G$23</f>
+        <f>'入力'!$G$24</f>
         <v/>
       </c>
       <c r="D8" s="4">
-        <f>'入力'!$H$23</f>
-        <v/>
-      </c>
-      <c r="E8" s="17">
-        <f>IF('入力'!$F$23&gt;0,'入力'!$B$23,0)</f>
-        <v/>
-      </c>
-      <c r="F8" s="17">
-        <f>IF('入力'!$G$23&gt;0,'入力'!$B$23,0)</f>
-        <v/>
-      </c>
-      <c r="G8" s="17">
-        <f>IF('入力'!$H$23&gt;0,'入力'!$B$23,0)</f>
-        <v/>
-      </c>
-      <c r="H8" s="17">
-        <f>'入力'!$B$23*'入力'!$F$23</f>
-        <v/>
-      </c>
-      <c r="I8" s="17">
-        <f>'入力'!$B$23*'入力'!$G$23</f>
-        <v/>
-      </c>
-      <c r="J8" s="17">
-        <f>'入力'!$B$23*'入力'!$H$23</f>
+        <f>'入力'!$H$24</f>
+        <v/>
+      </c>
+      <c r="E8" s="18">
+        <f>IF('入力'!$F$24&gt;0,'入力'!$B$24,0)</f>
+        <v/>
+      </c>
+      <c r="F8" s="18">
+        <f>IF('入力'!$G$24&gt;0,'入力'!$B$24,0)</f>
+        <v/>
+      </c>
+      <c r="G8" s="18">
+        <f>IF('入力'!$H$24&gt;0,'入力'!$B$24,0)</f>
+        <v/>
+      </c>
+      <c r="H8" s="18">
+        <f>'入力'!$B$24*'入力'!$F$24</f>
+        <v/>
+      </c>
+      <c r="I8" s="18">
+        <f>'入力'!$B$24*'入力'!$G$24</f>
+        <v/>
+      </c>
+      <c r="J8" s="18">
+        <f>'入力'!$B$24*'入力'!$H$24</f>
         <v/>
       </c>
     </row>
@@ -2232,39 +2269,39 @@
         </is>
       </c>
       <c r="B9" s="4">
-        <f>'入力'!$F$24</f>
+        <f>'入力'!$F$25</f>
         <v/>
       </c>
       <c r="C9" s="4">
-        <f>'入力'!$G$24</f>
+        <f>'入力'!$G$25</f>
         <v/>
       </c>
       <c r="D9" s="4">
-        <f>'入力'!$H$24</f>
-        <v/>
-      </c>
-      <c r="E9" s="17">
-        <f>IF('入力'!$F$24&gt;0,'入力'!$B$24,0)</f>
-        <v/>
-      </c>
-      <c r="F9" s="17">
-        <f>IF('入力'!$G$24&gt;0,'入力'!$B$24,0)</f>
-        <v/>
-      </c>
-      <c r="G9" s="17">
-        <f>IF('入力'!$H$24&gt;0,'入力'!$B$24,0)</f>
-        <v/>
-      </c>
-      <c r="H9" s="17">
-        <f>'入力'!$B$24*'入力'!$F$24</f>
-        <v/>
-      </c>
-      <c r="I9" s="17">
-        <f>'入力'!$B$24*'入力'!$G$24</f>
-        <v/>
-      </c>
-      <c r="J9" s="17">
-        <f>'入力'!$B$24*'入力'!$H$24</f>
+        <f>'入力'!$H$25</f>
+        <v/>
+      </c>
+      <c r="E9" s="18">
+        <f>IF('入力'!$F$25&gt;0,'入力'!$B$25,0)</f>
+        <v/>
+      </c>
+      <c r="F9" s="18">
+        <f>IF('入力'!$G$25&gt;0,'入力'!$B$25,0)</f>
+        <v/>
+      </c>
+      <c r="G9" s="18">
+        <f>IF('入力'!$H$25&gt;0,'入力'!$B$25,0)</f>
+        <v/>
+      </c>
+      <c r="H9" s="18">
+        <f>'入力'!$B$25*'入力'!$F$25</f>
+        <v/>
+      </c>
+      <c r="I9" s="18">
+        <f>'入力'!$B$25*'入力'!$G$25</f>
+        <v/>
+      </c>
+      <c r="J9" s="18">
+        <f>'入力'!$B$25*'入力'!$H$25</f>
         <v/>
       </c>
     </row>
@@ -2275,69 +2312,69 @@
         </is>
       </c>
       <c r="B10" s="4">
-        <f>'入力'!$F$25</f>
+        <f>'入力'!$F$26</f>
         <v/>
       </c>
       <c r="C10" s="4">
-        <f>'入力'!$G$25</f>
+        <f>'入力'!$G$26</f>
         <v/>
       </c>
       <c r="D10" s="4">
-        <f>'入力'!$H$25</f>
-        <v/>
-      </c>
-      <c r="E10" s="17">
-        <f>IF('入力'!$F$25&gt;0,'入力'!$B$25,0)</f>
-        <v/>
-      </c>
-      <c r="F10" s="17">
-        <f>IF('入力'!$G$25&gt;0,'入力'!$B$25,0)</f>
-        <v/>
-      </c>
-      <c r="G10" s="17">
-        <f>IF('入力'!$H$25&gt;0,'入力'!$B$25,0)</f>
-        <v/>
-      </c>
-      <c r="H10" s="17">
-        <f>'入力'!$B$25*'入力'!$F$25</f>
-        <v/>
-      </c>
-      <c r="I10" s="17">
-        <f>'入力'!$B$25*'入力'!$G$25</f>
-        <v/>
-      </c>
-      <c r="J10" s="17">
-        <f>'入力'!$B$25*'入力'!$H$25</f>
+        <f>'入力'!$H$26</f>
+        <v/>
+      </c>
+      <c r="E10" s="18">
+        <f>IF('入力'!$F$26&gt;0,'入力'!$B$26,0)</f>
+        <v/>
+      </c>
+      <c r="F10" s="18">
+        <f>IF('入力'!$G$26&gt;0,'入力'!$B$26,0)</f>
+        <v/>
+      </c>
+      <c r="G10" s="18">
+        <f>IF('入力'!$H$26&gt;0,'入力'!$B$26,0)</f>
+        <v/>
+      </c>
+      <c r="H10" s="18">
+        <f>'入力'!$B$26*'入力'!$F$26</f>
+        <v/>
+      </c>
+      <c r="I10" s="18">
+        <f>'入力'!$B$26*'入力'!$G$26</f>
+        <v/>
+      </c>
+      <c r="J10" s="18">
+        <f>'入力'!$B$26*'入力'!$H$26</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="E11" s="19">
+      <c r="E11" s="20">
         <f>SUM(E5:E10)</f>
         <v/>
       </c>
-      <c r="F11" s="19">
+      <c r="F11" s="20">
         <f>SUM(F5:F10)</f>
         <v/>
       </c>
-      <c r="G11" s="19">
+      <c r="G11" s="20">
         <f>SUM(G5:G10)</f>
         <v/>
       </c>
-      <c r="H11" s="19">
+      <c r="H11" s="20">
         <f>SUM(H5:H10)</f>
         <v/>
       </c>
-      <c r="I11" s="19">
+      <c r="I11" s="20">
         <f>SUM(I5:I10)</f>
         <v/>
       </c>
-      <c r="J11" s="19">
+      <c r="J11" s="20">
         <f>SUM(J5:J10)</f>
         <v/>
       </c>
@@ -2426,27 +2463,27 @@
           <t>① 未接触・潜在8人以上(重点医師)</t>
         </is>
       </c>
-      <c r="B6" s="20">
-        <f>'入力'!$B$20*'入力'!$F$20*'入力'!$D$20</f>
-        <v/>
-      </c>
-      <c r="C6" s="17">
+      <c r="B6" s="21">
+        <f>'入力'!$B$21*'入力'!$F$21*'入力'!$D$21</f>
+        <v/>
+      </c>
+      <c r="C6" s="18">
         <f>B6*unit_price</f>
         <v/>
       </c>
-      <c r="E6" s="20">
-        <f>'入力'!$B$20*'入力'!$G$20*'入力'!$D$20</f>
-        <v/>
-      </c>
-      <c r="F6" s="20">
-        <f>'入力'!$B$20*'入力'!$H$20*'入力'!$D$20</f>
-        <v/>
-      </c>
-      <c r="H6" s="17">
+      <c r="E6" s="21">
+        <f>'入力'!$B$21*'入力'!$G$21*'入力'!$D$21</f>
+        <v/>
+      </c>
+      <c r="F6" s="21">
+        <f>'入力'!$B$21*'入力'!$H$21*'入力'!$D$21</f>
+        <v/>
+      </c>
+      <c r="H6" s="18">
         <f>E6*unit_price</f>
         <v/>
       </c>
-      <c r="I6" s="17">
+      <c r="I6" s="18">
         <f>F6*unit_price</f>
         <v/>
       </c>
@@ -2457,27 +2494,27 @@
           <t>② 配信中・潜在8人以上(重点医師)</t>
         </is>
       </c>
-      <c r="B7" s="20">
-        <f>'入力'!$B$21*'入力'!$F$21*'入力'!$D$21</f>
-        <v/>
-      </c>
-      <c r="C7" s="17">
+      <c r="B7" s="21">
+        <f>'入力'!$B$22*'入力'!$F$22*'入力'!$D$22</f>
+        <v/>
+      </c>
+      <c r="C7" s="18">
         <f>B7*unit_price</f>
         <v/>
       </c>
-      <c r="E7" s="20">
-        <f>'入力'!$B$21*'入力'!$G$21*'入力'!$D$21</f>
-        <v/>
-      </c>
-      <c r="F7" s="20">
-        <f>'入力'!$B$21*'入力'!$H$21*'入力'!$D$21</f>
-        <v/>
-      </c>
-      <c r="H7" s="17">
+      <c r="E7" s="21">
+        <f>'入力'!$B$22*'入力'!$G$22*'入力'!$D$22</f>
+        <v/>
+      </c>
+      <c r="F7" s="21">
+        <f>'入力'!$B$22*'入力'!$H$22*'入力'!$D$22</f>
+        <v/>
+      </c>
+      <c r="H7" s="18">
         <f>E7*unit_price</f>
         <v/>
       </c>
-      <c r="I7" s="17">
+      <c r="I7" s="18">
         <f>F7*unit_price</f>
         <v/>
       </c>
@@ -2488,27 +2525,27 @@
           <t>③ 配信中・潜在0〜2人(財源)</t>
         </is>
       </c>
-      <c r="B8" s="20">
-        <f>'入力'!$B$22*'入力'!$F$22*'入力'!$D$22</f>
-        <v/>
-      </c>
-      <c r="C8" s="17">
+      <c r="B8" s="21">
+        <f>'入力'!$B$23*'入力'!$F$23*'入力'!$D$23</f>
+        <v/>
+      </c>
+      <c r="C8" s="18">
         <f>B8*unit_price</f>
         <v/>
       </c>
-      <c r="E8" s="20">
-        <f>'入力'!$B$22*'入力'!$G$22*'入力'!$D$22</f>
-        <v/>
-      </c>
-      <c r="F8" s="20">
-        <f>'入力'!$B$22*'入力'!$H$22*'入力'!$D$22</f>
-        <v/>
-      </c>
-      <c r="H8" s="17">
+      <c r="E8" s="21">
+        <f>'入力'!$B$23*'入力'!$G$23*'入力'!$D$23</f>
+        <v/>
+      </c>
+      <c r="F8" s="21">
+        <f>'入力'!$B$23*'入力'!$H$23*'入力'!$D$23</f>
+        <v/>
+      </c>
+      <c r="H8" s="18">
         <f>E8*unit_price</f>
         <v/>
       </c>
-      <c r="I8" s="17">
+      <c r="I8" s="18">
         <f>F8*unit_price</f>
         <v/>
       </c>
@@ -2519,27 +2556,27 @@
           <t>④ MR面談あり・潜在8人以上(重点医師、配信中)</t>
         </is>
       </c>
-      <c r="B9" s="20">
-        <f>'入力'!$B$23*'入力'!$F$23*'入力'!$D$23</f>
-        <v/>
-      </c>
-      <c r="C9" s="17">
+      <c r="B9" s="21">
+        <f>'入力'!$B$24*'入力'!$F$24*'入力'!$D$24</f>
+        <v/>
+      </c>
+      <c r="C9" s="18">
         <f>B9*unit_price</f>
         <v/>
       </c>
-      <c r="E9" s="20">
-        <f>'入力'!$B$23*'入力'!$G$23*'入力'!$D$23</f>
-        <v/>
-      </c>
-      <c r="F9" s="20">
-        <f>'入力'!$B$23*'入力'!$H$23*'入力'!$D$23</f>
-        <v/>
-      </c>
-      <c r="H9" s="17">
+      <c r="E9" s="21">
+        <f>'入力'!$B$24*'入力'!$G$24*'入力'!$D$24</f>
+        <v/>
+      </c>
+      <c r="F9" s="21">
+        <f>'入力'!$B$24*'入力'!$H$24*'入力'!$D$24</f>
+        <v/>
+      </c>
+      <c r="H9" s="18">
         <f>E9*unit_price</f>
         <v/>
       </c>
-      <c r="I9" s="17">
+      <c r="I9" s="18">
         <f>F9*unit_price</f>
         <v/>
       </c>
@@ -2550,27 +2587,27 @@
           <t>⑤ 未接触・潜在5〜7人(B案で追加)</t>
         </is>
       </c>
-      <c r="B10" s="20">
-        <f>'入力'!$B$24*'入力'!$F$24*'入力'!$D$24</f>
-        <v/>
-      </c>
-      <c r="C10" s="17">
+      <c r="B10" s="21">
+        <f>'入力'!$B$25*'入力'!$F$25*'入力'!$D$25</f>
+        <v/>
+      </c>
+      <c r="C10" s="18">
         <f>B10*unit_price</f>
         <v/>
       </c>
-      <c r="E10" s="20">
-        <f>'入力'!$B$24*'入力'!$G$24*'入力'!$D$24</f>
-        <v/>
-      </c>
-      <c r="F10" s="20">
-        <f>'入力'!$B$24*'入力'!$H$24*'入力'!$D$24</f>
-        <v/>
-      </c>
-      <c r="H10" s="17">
+      <c r="E10" s="21">
+        <f>'入力'!$B$25*'入力'!$G$25*'入力'!$D$25</f>
+        <v/>
+      </c>
+      <c r="F10" s="21">
+        <f>'入力'!$B$25*'入力'!$H$25*'入力'!$D$25</f>
+        <v/>
+      </c>
+      <c r="H10" s="18">
         <f>E10*unit_price</f>
         <v/>
       </c>
-      <c r="I10" s="17">
+      <c r="I10" s="18">
         <f>F10*unit_price</f>
         <v/>
       </c>
@@ -2581,58 +2618,58 @@
           <t>その他の配信中(変更なし)</t>
         </is>
       </c>
-      <c r="B11" s="20">
-        <f>'入力'!$B$25*'入力'!$F$25*'入力'!$D$25</f>
-        <v/>
-      </c>
-      <c r="C11" s="17">
+      <c r="B11" s="21">
+        <f>'入力'!$B$26*'入力'!$F$26*'入力'!$D$26</f>
+        <v/>
+      </c>
+      <c r="C11" s="18">
         <f>B11*unit_price</f>
         <v/>
       </c>
-      <c r="E11" s="20">
-        <f>'入力'!$B$25*'入力'!$G$25*'入力'!$D$25</f>
-        <v/>
-      </c>
-      <c r="F11" s="20">
-        <f>'入力'!$B$25*'入力'!$H$25*'入力'!$D$25</f>
-        <v/>
-      </c>
-      <c r="H11" s="17">
+      <c r="E11" s="21">
+        <f>'入力'!$B$26*'入力'!$G$26*'入力'!$D$26</f>
+        <v/>
+      </c>
+      <c r="F11" s="21">
+        <f>'入力'!$B$26*'入力'!$H$26*'入力'!$D$26</f>
+        <v/>
+      </c>
+      <c r="H11" s="18">
         <f>E11*unit_price</f>
         <v/>
       </c>
-      <c r="I11" s="17">
+      <c r="I11" s="18">
         <f>F11*unit_price</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>既読費用 合計</t>
         </is>
       </c>
-      <c r="B12" s="19">
+      <c r="B12" s="20">
         <f>SUM(B6:B11)</f>
         <v/>
       </c>
-      <c r="C12" s="19">
+      <c r="C12" s="20">
         <f>SUM(C6:C11)</f>
         <v/>
       </c>
-      <c r="E12" s="19">
+      <c r="E12" s="20">
         <f>SUM(E6:E11)</f>
         <v/>
       </c>
-      <c r="F12" s="19">
+      <c r="F12" s="20">
         <f>SUM(F6:F11)</f>
         <v/>
       </c>
-      <c r="H12" s="19">
+      <c r="H12" s="20">
         <f>SUM(H6:H11)</f>
         <v/>
       </c>
-      <c r="I12" s="19">
+      <c r="I12" s="20">
         <f>SUM(I6:I11)</f>
         <v/>
       </c>
@@ -2643,59 +2680,59 @@
           <t>制作費・運用費(未確認)</t>
         </is>
       </c>
-      <c r="C13" s="17" t="n">
+      <c r="C13" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="17">
+      <c r="H13" s="18">
         <f>prod_cost+ops_cost</f>
         <v/>
       </c>
-      <c r="I13" s="17">
+      <c r="I13" s="18">
         <f>prod_cost+ops_cost</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>総費用</t>
         </is>
       </c>
-      <c r="C14" s="19">
+      <c r="C14" s="20">
         <f>C12+C13</f>
         <v/>
       </c>
-      <c r="H14" s="19">
+      <c r="H14" s="20">
         <f>H12+H13</f>
         <v/>
       </c>
-      <c r="I14" s="19">
+      <c r="I14" s="20">
         <f>I12+I13</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>現状からの追加費用</t>
         </is>
       </c>
-      <c r="H15" s="19">
+      <c r="H15" s="20">
         <f>H14-C14</f>
         <v/>
       </c>
-      <c r="I15" s="19">
+      <c r="I15" s="20">
         <f>I14-C14</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>予算判定(A案は現状費用以内か)</t>
         </is>
       </c>
-      <c r="H16" s="18">
+      <c r="H16" s="19">
         <f>IF(H14&lt;=C14,"予算内","予算超過")</f>
         <v/>
       </c>
@@ -2744,7 +2781,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="H3" s="21" t="inlineStr">
+      <c r="H3" s="22" t="inlineStr">
         <is>
           <t>追加処方患者(人)</t>
         </is>
@@ -2823,52 +2860,52 @@
           <t>① 未接触・潜在8人以上(重点医師)</t>
         </is>
       </c>
-      <c r="B5" s="22">
-        <f>'入力'!$C$20/'入力'!$B$20</f>
-        <v/>
-      </c>
-      <c r="C5" s="23">
-        <f>IF(OR('入力'!$E$20="",'入力'!$F$20=0),0,1-(1-'入力'!$E$20)^('入力'!$F$20/10))</f>
-        <v/>
-      </c>
-      <c r="D5" s="23">
-        <f>IF(OR('入力'!$E$20="",'入力'!$G$20=0),0,1-(1-'入力'!$E$20)^('入力'!$G$20/10))</f>
-        <v/>
-      </c>
-      <c r="E5" s="23">
-        <f>IF(OR('入力'!$E$20="",'入力'!$H$20=0),0,1-(1-'入力'!$E$20)^('入力'!$H$20/10))</f>
-        <v/>
-      </c>
-      <c r="F5" s="20">
-        <f>IF('入力'!$E$20="",0,'入力'!$B$20*(D5-C5))</f>
-        <v/>
-      </c>
-      <c r="G5" s="20">
-        <f>IF('入力'!$E$20="",0,'入力'!$B$20*(E5-C5))</f>
-        <v/>
-      </c>
-      <c r="H5" s="20">
-        <f>F5*B5*'入力'!$I$20*conv_low</f>
-        <v/>
-      </c>
-      <c r="I5" s="20">
-        <f>F5*B5*'入力'!$I$20*conv_base</f>
-        <v/>
-      </c>
-      <c r="J5" s="20">
-        <f>F5*B5*'入力'!$I$20*conv_high</f>
-        <v/>
-      </c>
-      <c r="K5" s="20">
-        <f>G5*B5*'入力'!$I$20*conv_low</f>
-        <v/>
-      </c>
-      <c r="L5" s="20">
-        <f>G5*B5*'入力'!$I$20*conv_base</f>
-        <v/>
-      </c>
-      <c r="M5" s="20">
-        <f>G5*B5*'入力'!$I$20*conv_high</f>
+      <c r="B5" s="23">
+        <f>'入力'!$C$21/'入力'!$B$21</f>
+        <v/>
+      </c>
+      <c r="C5" s="24">
+        <f>IF(OR('入力'!$E$21="",'入力'!$F$21=0),0,1-(1-'入力'!$E$21)^('入力'!$F$21/10))</f>
+        <v/>
+      </c>
+      <c r="D5" s="24">
+        <f>IF(OR('入力'!$E$21="",'入力'!$G$21=0),0,1-(1-'入力'!$E$21)^('入力'!$G$21/10))</f>
+        <v/>
+      </c>
+      <c r="E5" s="24">
+        <f>IF(OR('入力'!$E$21="",'入力'!$H$21=0),0,1-(1-'入力'!$E$21)^('入力'!$H$21/10))</f>
+        <v/>
+      </c>
+      <c r="F5" s="21">
+        <f>IF('入力'!$E$21="",0,'入力'!$B$21*(D5-C5))</f>
+        <v/>
+      </c>
+      <c r="G5" s="21">
+        <f>IF('入力'!$E$21="",0,'入力'!$B$21*(E5-C5))</f>
+        <v/>
+      </c>
+      <c r="H5" s="21">
+        <f>F5*B5*'入力'!$I$21*conv_low</f>
+        <v/>
+      </c>
+      <c r="I5" s="21">
+        <f>F5*B5*'入力'!$I$21*conv_base</f>
+        <v/>
+      </c>
+      <c r="J5" s="21">
+        <f>F5*B5*'入力'!$I$21*conv_high</f>
+        <v/>
+      </c>
+      <c r="K5" s="21">
+        <f>G5*B5*'入力'!$I$21*conv_low</f>
+        <v/>
+      </c>
+      <c r="L5" s="21">
+        <f>G5*B5*'入力'!$I$21*conv_base</f>
+        <v/>
+      </c>
+      <c r="M5" s="21">
+        <f>G5*B5*'入力'!$I$21*conv_high</f>
         <v/>
       </c>
     </row>
@@ -2878,52 +2915,52 @@
           <t>② 配信中・潜在8人以上(重点医師)</t>
         </is>
       </c>
-      <c r="B6" s="22">
-        <f>'入力'!$C$21/'入力'!$B$21</f>
-        <v/>
-      </c>
-      <c r="C6" s="23">
-        <f>IF(OR('入力'!$E$21="",'入力'!$F$21=0),0,1-(1-'入力'!$E$21)^('入力'!$F$21/10))</f>
-        <v/>
-      </c>
-      <c r="D6" s="23">
-        <f>IF(OR('入力'!$E$21="",'入力'!$G$21=0),0,1-(1-'入力'!$E$21)^('入力'!$G$21/10))</f>
-        <v/>
-      </c>
-      <c r="E6" s="23">
-        <f>IF(OR('入力'!$E$21="",'入力'!$H$21=0),0,1-(1-'入力'!$E$21)^('入力'!$H$21/10))</f>
-        <v/>
-      </c>
-      <c r="F6" s="20">
-        <f>IF('入力'!$E$21="",0,'入力'!$B$21*(D6-C6))</f>
-        <v/>
-      </c>
-      <c r="G6" s="20">
-        <f>IF('入力'!$E$21="",0,'入力'!$B$21*(E6-C6))</f>
-        <v/>
-      </c>
-      <c r="H6" s="20">
-        <f>F6*B6*'入力'!$I$21*conv_low</f>
-        <v/>
-      </c>
-      <c r="I6" s="20">
-        <f>F6*B6*'入力'!$I$21*conv_base</f>
-        <v/>
-      </c>
-      <c r="J6" s="20">
-        <f>F6*B6*'入力'!$I$21*conv_high</f>
-        <v/>
-      </c>
-      <c r="K6" s="20">
-        <f>G6*B6*'入力'!$I$21*conv_low</f>
-        <v/>
-      </c>
-      <c r="L6" s="20">
-        <f>G6*B6*'入力'!$I$21*conv_base</f>
-        <v/>
-      </c>
-      <c r="M6" s="20">
-        <f>G6*B6*'入力'!$I$21*conv_high</f>
+      <c r="B6" s="23">
+        <f>'入力'!$C$22/'入力'!$B$22</f>
+        <v/>
+      </c>
+      <c r="C6" s="24">
+        <f>IF(OR('入力'!$E$22="",'入力'!$F$22=0),0,1-(1-'入力'!$E$22)^('入力'!$F$22/10))</f>
+        <v/>
+      </c>
+      <c r="D6" s="24">
+        <f>IF(OR('入力'!$E$22="",'入力'!$G$22=0),0,1-(1-'入力'!$E$22)^('入力'!$G$22/10))</f>
+        <v/>
+      </c>
+      <c r="E6" s="24">
+        <f>IF(OR('入力'!$E$22="",'入力'!$H$22=0),0,1-(1-'入力'!$E$22)^('入力'!$H$22/10))</f>
+        <v/>
+      </c>
+      <c r="F6" s="21">
+        <f>IF('入力'!$E$22="",0,'入力'!$B$22*(D6-C6))</f>
+        <v/>
+      </c>
+      <c r="G6" s="21">
+        <f>IF('入力'!$E$22="",0,'入力'!$B$22*(E6-C6))</f>
+        <v/>
+      </c>
+      <c r="H6" s="21">
+        <f>F6*B6*'入力'!$I$22*conv_low</f>
+        <v/>
+      </c>
+      <c r="I6" s="21">
+        <f>F6*B6*'入力'!$I$22*conv_base</f>
+        <v/>
+      </c>
+      <c r="J6" s="21">
+        <f>F6*B6*'入力'!$I$22*conv_high</f>
+        <v/>
+      </c>
+      <c r="K6" s="21">
+        <f>G6*B6*'入力'!$I$22*conv_low</f>
+        <v/>
+      </c>
+      <c r="L6" s="21">
+        <f>G6*B6*'入力'!$I$22*conv_base</f>
+        <v/>
+      </c>
+      <c r="M6" s="21">
+        <f>G6*B6*'入力'!$I$22*conv_high</f>
         <v/>
       </c>
     </row>
@@ -2933,52 +2970,52 @@
           <t>③ 配信中・潜在0〜2人(財源)</t>
         </is>
       </c>
-      <c r="B7" s="22">
-        <f>'入力'!$C$22/'入力'!$B$22</f>
-        <v/>
-      </c>
-      <c r="C7" s="23">
-        <f>IF(OR('入力'!$E$22="",'入力'!$F$22=0),0,1-(1-'入力'!$E$22)^('入力'!$F$22/10))</f>
-        <v/>
-      </c>
-      <c r="D7" s="23">
-        <f>IF(OR('入力'!$E$22="",'入力'!$G$22=0),0,1-(1-'入力'!$E$22)^('入力'!$G$22/10))</f>
-        <v/>
-      </c>
-      <c r="E7" s="23">
-        <f>IF(OR('入力'!$E$22="",'入力'!$H$22=0),0,1-(1-'入力'!$E$22)^('入力'!$H$22/10))</f>
-        <v/>
-      </c>
-      <c r="F7" s="20">
-        <f>IF('入力'!$E$22="",0,'入力'!$B$22*(D7-C7))</f>
-        <v/>
-      </c>
-      <c r="G7" s="20">
-        <f>IF('入力'!$E$22="",0,'入力'!$B$22*(E7-C7))</f>
-        <v/>
-      </c>
-      <c r="H7" s="20">
-        <f>F7*B7*'入力'!$I$22*conv_low</f>
-        <v/>
-      </c>
-      <c r="I7" s="20">
-        <f>F7*B7*'入力'!$I$22*conv_base</f>
-        <v/>
-      </c>
-      <c r="J7" s="20">
-        <f>F7*B7*'入力'!$I$22*conv_high</f>
-        <v/>
-      </c>
-      <c r="K7" s="20">
-        <f>G7*B7*'入力'!$I$22*conv_low</f>
-        <v/>
-      </c>
-      <c r="L7" s="20">
-        <f>G7*B7*'入力'!$I$22*conv_base</f>
-        <v/>
-      </c>
-      <c r="M7" s="20">
-        <f>G7*B7*'入力'!$I$22*conv_high</f>
+      <c r="B7" s="23">
+        <f>'入力'!$C$23/'入力'!$B$23</f>
+        <v/>
+      </c>
+      <c r="C7" s="24">
+        <f>IF(OR('入力'!$E$23="",'入力'!$F$23=0),0,1-(1-'入力'!$E$23)^('入力'!$F$23/10))</f>
+        <v/>
+      </c>
+      <c r="D7" s="24">
+        <f>IF(OR('入力'!$E$23="",'入力'!$G$23=0),0,1-(1-'入力'!$E$23)^('入力'!$G$23/10))</f>
+        <v/>
+      </c>
+      <c r="E7" s="24">
+        <f>IF(OR('入力'!$E$23="",'入力'!$H$23=0),0,1-(1-'入力'!$E$23)^('入力'!$H$23/10))</f>
+        <v/>
+      </c>
+      <c r="F7" s="21">
+        <f>IF('入力'!$E$23="",0,'入力'!$B$23*(D7-C7))</f>
+        <v/>
+      </c>
+      <c r="G7" s="21">
+        <f>IF('入力'!$E$23="",0,'入力'!$B$23*(E7-C7))</f>
+        <v/>
+      </c>
+      <c r="H7" s="21">
+        <f>F7*B7*'入力'!$I$23*conv_low</f>
+        <v/>
+      </c>
+      <c r="I7" s="21">
+        <f>F7*B7*'入力'!$I$23*conv_base</f>
+        <v/>
+      </c>
+      <c r="J7" s="21">
+        <f>F7*B7*'入力'!$I$23*conv_high</f>
+        <v/>
+      </c>
+      <c r="K7" s="21">
+        <f>G7*B7*'入力'!$I$23*conv_low</f>
+        <v/>
+      </c>
+      <c r="L7" s="21">
+        <f>G7*B7*'入力'!$I$23*conv_base</f>
+        <v/>
+      </c>
+      <c r="M7" s="21">
+        <f>G7*B7*'入力'!$I$23*conv_high</f>
         <v/>
       </c>
     </row>
@@ -2988,52 +3025,52 @@
           <t>④ MR面談あり・潜在8人以上(重点医師、配信中)</t>
         </is>
       </c>
-      <c r="B8" s="22">
-        <f>'入力'!$C$23/'入力'!$B$23</f>
-        <v/>
-      </c>
-      <c r="C8" s="23">
-        <f>IF(OR('入力'!$E$23="",'入力'!$F$23=0),0,1-(1-'入力'!$E$23)^('入力'!$F$23/10))</f>
-        <v/>
-      </c>
-      <c r="D8" s="23">
-        <f>IF(OR('入力'!$E$23="",'入力'!$G$23=0),0,1-(1-'入力'!$E$23)^('入力'!$G$23/10))</f>
-        <v/>
-      </c>
-      <c r="E8" s="23">
-        <f>IF(OR('入力'!$E$23="",'入力'!$H$23=0),0,1-(1-'入力'!$E$23)^('入力'!$H$23/10))</f>
-        <v/>
-      </c>
-      <c r="F8" s="20">
-        <f>IF('入力'!$E$23="",0,'入力'!$B$23*(D8-C8))</f>
-        <v/>
-      </c>
-      <c r="G8" s="20">
-        <f>IF('入力'!$E$23="",0,'入力'!$B$23*(E8-C8))</f>
-        <v/>
-      </c>
-      <c r="H8" s="20">
-        <f>F8*B8*'入力'!$I$23*conv_low</f>
-        <v/>
-      </c>
-      <c r="I8" s="20">
-        <f>F8*B8*'入力'!$I$23*conv_base</f>
-        <v/>
-      </c>
-      <c r="J8" s="20">
-        <f>F8*B8*'入力'!$I$23*conv_high</f>
-        <v/>
-      </c>
-      <c r="K8" s="20">
-        <f>G8*B8*'入力'!$I$23*conv_low</f>
-        <v/>
-      </c>
-      <c r="L8" s="20">
-        <f>G8*B8*'入力'!$I$23*conv_base</f>
-        <v/>
-      </c>
-      <c r="M8" s="20">
-        <f>G8*B8*'入力'!$I$23*conv_high</f>
+      <c r="B8" s="23">
+        <f>'入力'!$C$24/'入力'!$B$24</f>
+        <v/>
+      </c>
+      <c r="C8" s="24">
+        <f>IF(OR('入力'!$E$24="",'入力'!$F$24=0),0,1-(1-'入力'!$E$24)^('入力'!$F$24/10))</f>
+        <v/>
+      </c>
+      <c r="D8" s="24">
+        <f>IF(OR('入力'!$E$24="",'入力'!$G$24=0),0,1-(1-'入力'!$E$24)^('入力'!$G$24/10))</f>
+        <v/>
+      </c>
+      <c r="E8" s="24">
+        <f>IF(OR('入力'!$E$24="",'入力'!$H$24=0),0,1-(1-'入力'!$E$24)^('入力'!$H$24/10))</f>
+        <v/>
+      </c>
+      <c r="F8" s="21">
+        <f>IF('入力'!$E$24="",0,'入力'!$B$24*(D8-C8))</f>
+        <v/>
+      </c>
+      <c r="G8" s="21">
+        <f>IF('入力'!$E$24="",0,'入力'!$B$24*(E8-C8))</f>
+        <v/>
+      </c>
+      <c r="H8" s="21">
+        <f>F8*B8*'入力'!$I$24*conv_low</f>
+        <v/>
+      </c>
+      <c r="I8" s="21">
+        <f>F8*B8*'入力'!$I$24*conv_base</f>
+        <v/>
+      </c>
+      <c r="J8" s="21">
+        <f>F8*B8*'入力'!$I$24*conv_high</f>
+        <v/>
+      </c>
+      <c r="K8" s="21">
+        <f>G8*B8*'入力'!$I$24*conv_low</f>
+        <v/>
+      </c>
+      <c r="L8" s="21">
+        <f>G8*B8*'入力'!$I$24*conv_base</f>
+        <v/>
+      </c>
+      <c r="M8" s="21">
+        <f>G8*B8*'入力'!$I$24*conv_high</f>
         <v/>
       </c>
     </row>
@@ -3043,52 +3080,52 @@
           <t>⑤ 未接触・潜在5〜7人(B案で追加)</t>
         </is>
       </c>
-      <c r="B9" s="22">
-        <f>'入力'!$C$24/'入力'!$B$24</f>
-        <v/>
-      </c>
-      <c r="C9" s="23">
-        <f>IF(OR('入力'!$E$24="",'入力'!$F$24=0),0,1-(1-'入力'!$E$24)^('入力'!$F$24/10))</f>
-        <v/>
-      </c>
-      <c r="D9" s="23">
-        <f>IF(OR('入力'!$E$24="",'入力'!$G$24=0),0,1-(1-'入力'!$E$24)^('入力'!$G$24/10))</f>
-        <v/>
-      </c>
-      <c r="E9" s="23">
-        <f>IF(OR('入力'!$E$24="",'入力'!$H$24=0),0,1-(1-'入力'!$E$24)^('入力'!$H$24/10))</f>
-        <v/>
-      </c>
-      <c r="F9" s="20">
-        <f>IF('入力'!$E$24="",0,'入力'!$B$24*(D9-C9))</f>
-        <v/>
-      </c>
-      <c r="G9" s="20">
-        <f>IF('入力'!$E$24="",0,'入力'!$B$24*(E9-C9))</f>
-        <v/>
-      </c>
-      <c r="H9" s="20">
-        <f>F9*B9*'入力'!$I$24*conv_low</f>
-        <v/>
-      </c>
-      <c r="I9" s="20">
-        <f>F9*B9*'入力'!$I$24*conv_base</f>
-        <v/>
-      </c>
-      <c r="J9" s="20">
-        <f>F9*B9*'入力'!$I$24*conv_high</f>
-        <v/>
-      </c>
-      <c r="K9" s="20">
-        <f>G9*B9*'入力'!$I$24*conv_low</f>
-        <v/>
-      </c>
-      <c r="L9" s="20">
-        <f>G9*B9*'入力'!$I$24*conv_base</f>
-        <v/>
-      </c>
-      <c r="M9" s="20">
-        <f>G9*B9*'入力'!$I$24*conv_high</f>
+      <c r="B9" s="23">
+        <f>'入力'!$C$25/'入力'!$B$25</f>
+        <v/>
+      </c>
+      <c r="C9" s="24">
+        <f>IF(OR('入力'!$E$25="",'入力'!$F$25=0),0,1-(1-'入力'!$E$25)^('入力'!$F$25/10))</f>
+        <v/>
+      </c>
+      <c r="D9" s="24">
+        <f>IF(OR('入力'!$E$25="",'入力'!$G$25=0),0,1-(1-'入力'!$E$25)^('入力'!$G$25/10))</f>
+        <v/>
+      </c>
+      <c r="E9" s="24">
+        <f>IF(OR('入力'!$E$25="",'入力'!$H$25=0),0,1-(1-'入力'!$E$25)^('入力'!$H$25/10))</f>
+        <v/>
+      </c>
+      <c r="F9" s="21">
+        <f>IF('入力'!$E$25="",0,'入力'!$B$25*(D9-C9))</f>
+        <v/>
+      </c>
+      <c r="G9" s="21">
+        <f>IF('入力'!$E$25="",0,'入力'!$B$25*(E9-C9))</f>
+        <v/>
+      </c>
+      <c r="H9" s="21">
+        <f>F9*B9*'入力'!$I$25*conv_low</f>
+        <v/>
+      </c>
+      <c r="I9" s="21">
+        <f>F9*B9*'入力'!$I$25*conv_base</f>
+        <v/>
+      </c>
+      <c r="J9" s="21">
+        <f>F9*B9*'入力'!$I$25*conv_high</f>
+        <v/>
+      </c>
+      <c r="K9" s="21">
+        <f>G9*B9*'入力'!$I$25*conv_low</f>
+        <v/>
+      </c>
+      <c r="L9" s="21">
+        <f>G9*B9*'入力'!$I$25*conv_base</f>
+        <v/>
+      </c>
+      <c r="M9" s="21">
+        <f>G9*B9*'入力'!$I$25*conv_high</f>
         <v/>
       </c>
     </row>
@@ -3098,122 +3135,122 @@
           <t>その他の配信中(変更なし)</t>
         </is>
       </c>
-      <c r="B10" s="22">
-        <f>'入力'!$C$25/'入力'!$B$25</f>
-        <v/>
-      </c>
-      <c r="C10" s="23">
-        <f>IF(OR('入力'!$E$25="",'入力'!$F$25=0),0,1-(1-'入力'!$E$25)^('入力'!$F$25/10))</f>
-        <v/>
-      </c>
-      <c r="D10" s="23">
-        <f>IF(OR('入力'!$E$25="",'入力'!$G$25=0),0,1-(1-'入力'!$E$25)^('入力'!$G$25/10))</f>
-        <v/>
-      </c>
-      <c r="E10" s="23">
-        <f>IF(OR('入力'!$E$25="",'入力'!$H$25=0),0,1-(1-'入力'!$E$25)^('入力'!$H$25/10))</f>
-        <v/>
-      </c>
-      <c r="F10" s="20">
-        <f>IF('入力'!$E$25="",0,'入力'!$B$25*(D10-C10))</f>
-        <v/>
-      </c>
-      <c r="G10" s="20">
-        <f>IF('入力'!$E$25="",0,'入力'!$B$25*(E10-C10))</f>
-        <v/>
-      </c>
-      <c r="H10" s="20">
-        <f>F10*B10*'入力'!$I$25*conv_low</f>
-        <v/>
-      </c>
-      <c r="I10" s="20">
-        <f>F10*B10*'入力'!$I$25*conv_base</f>
-        <v/>
-      </c>
-      <c r="J10" s="20">
-        <f>F10*B10*'入力'!$I$25*conv_high</f>
-        <v/>
-      </c>
-      <c r="K10" s="20">
-        <f>G10*B10*'入力'!$I$25*conv_low</f>
-        <v/>
-      </c>
-      <c r="L10" s="20">
-        <f>G10*B10*'入力'!$I$25*conv_base</f>
-        <v/>
-      </c>
-      <c r="M10" s="20">
-        <f>G10*B10*'入力'!$I$25*conv_high</f>
+      <c r="B10" s="23">
+        <f>'入力'!$C$26/'入力'!$B$26</f>
+        <v/>
+      </c>
+      <c r="C10" s="24">
+        <f>IF(OR('入力'!$E$26="",'入力'!$F$26=0),0,1-(1-'入力'!$E$26)^('入力'!$F$26/10))</f>
+        <v/>
+      </c>
+      <c r="D10" s="24">
+        <f>IF(OR('入力'!$E$26="",'入力'!$G$26=0),0,1-(1-'入力'!$E$26)^('入力'!$G$26/10))</f>
+        <v/>
+      </c>
+      <c r="E10" s="24">
+        <f>IF(OR('入力'!$E$26="",'入力'!$H$26=0),0,1-(1-'入力'!$E$26)^('入力'!$H$26/10))</f>
+        <v/>
+      </c>
+      <c r="F10" s="21">
+        <f>IF('入力'!$E$26="",0,'入力'!$B$26*(D10-C10))</f>
+        <v/>
+      </c>
+      <c r="G10" s="21">
+        <f>IF('入力'!$E$26="",0,'入力'!$B$26*(E10-C10))</f>
+        <v/>
+      </c>
+      <c r="H10" s="21">
+        <f>F10*B10*'入力'!$I$26*conv_low</f>
+        <v/>
+      </c>
+      <c r="I10" s="21">
+        <f>F10*B10*'入力'!$I$26*conv_base</f>
+        <v/>
+      </c>
+      <c r="J10" s="21">
+        <f>F10*B10*'入力'!$I$26*conv_high</f>
+        <v/>
+      </c>
+      <c r="K10" s="21">
+        <f>G10*B10*'入力'!$I$26*conv_low</f>
+        <v/>
+      </c>
+      <c r="L10" s="21">
+        <f>G10*B10*'入力'!$I$26*conv_base</f>
+        <v/>
+      </c>
+      <c r="M10" s="21">
+        <f>G10*B10*'入力'!$I$26*conv_high</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>追加処方患者 合計</t>
         </is>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="25">
         <f>SUM(F5:F10)</f>
         <v/>
       </c>
-      <c r="G11" s="24">
+      <c r="G11" s="25">
         <f>SUM(G5:G10)</f>
         <v/>
       </c>
-      <c r="H11" s="24">
+      <c r="H11" s="25">
         <f>SUM(H5:H10)</f>
         <v/>
       </c>
-      <c r="I11" s="24">
+      <c r="I11" s="25">
         <f>SUM(I5:I10)</f>
         <v/>
       </c>
-      <c r="J11" s="24">
+      <c r="J11" s="25">
         <f>SUM(J5:J10)</f>
         <v/>
       </c>
-      <c r="K11" s="24">
+      <c r="K11" s="25">
         <f>SUM(K5:K10)</f>
         <v/>
       </c>
-      <c r="L11" s="24">
+      <c r="L11" s="25">
         <f>SUM(L5:L10)</f>
         <v/>
       </c>
-      <c r="M11" s="24">
+      <c r="M11" s="25">
         <f>SUM(M5:M10)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
-        <is>
-          <t>追加売上(円) = 追加処方患者 × 処方患者1人あたり年間売上</t>
-        </is>
-      </c>
-      <c r="H12" s="19">
-        <f>H11*sales_per_pt</f>
-        <v/>
-      </c>
-      <c r="I12" s="19">
-        <f>I11*sales_per_pt</f>
-        <v/>
-      </c>
-      <c r="J12" s="19">
-        <f>J11*sales_per_pt</f>
-        <v/>
-      </c>
-      <c r="K12" s="19">
-        <f>K11*sales_per_pt</f>
-        <v/>
-      </c>
-      <c r="L12" s="19">
-        <f>L11*sales_per_pt</f>
-        <v/>
-      </c>
-      <c r="M12" s="19">
-        <f>M11*sales_per_pt</f>
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>全国換算の追加売上(円) = 追加処方患者 × 全国換算の倍率 × 処方患者1人あたり年間売上</t>
+        </is>
+      </c>
+      <c r="H12" s="20">
+        <f>H11*scale*sales_per_pt</f>
+        <v/>
+      </c>
+      <c r="I12" s="20">
+        <f>I11*scale*sales_per_pt</f>
+        <v/>
+      </c>
+      <c r="J12" s="20">
+        <f>J11*scale*sales_per_pt</f>
+        <v/>
+      </c>
+      <c r="K12" s="20">
+        <f>K11*scale*sales_per_pt</f>
+        <v/>
+      </c>
+      <c r="L12" s="20">
+        <f>L11*scale*sales_per_pt</f>
+        <v/>
+      </c>
+      <c r="M12" s="20">
+        <f>M11*scale*sales_per_pt</f>
         <v/>
       </c>
     </row>
@@ -3228,10 +3265,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
@@ -3252,6 +3289,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="22" t="inlineStr">
+        <is>
+          <t>回答医師5,000名(試算の基礎)</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -3285,19 +3329,19 @@
           <t>配信対象医師数(名)</t>
         </is>
       </c>
-      <c r="B5" s="17">
+      <c r="B5" s="18">
         <f>'③配信計画'!E11</f>
         <v/>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="18">
         <f>'③配信計画'!F11</f>
         <v/>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="18">
         <f>'③配信計画'!G11</f>
         <v/>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="18">
         <f>D5-C5</f>
         <v/>
       </c>
@@ -3308,19 +3352,19 @@
           <t>配信件数(件)</t>
         </is>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="18">
         <f>'③配信計画'!H11</f>
         <v/>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="18">
         <f>'③配信計画'!I11</f>
         <v/>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="18">
         <f>'③配信計画'!J11</f>
         <v/>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="18">
         <f>D6-C6</f>
         <v/>
       </c>
@@ -3331,19 +3375,19 @@
           <t>想定既読件数(件)</t>
         </is>
       </c>
-      <c r="B7" s="17">
+      <c r="B7" s="18">
         <f>'④費用計算'!B12</f>
         <v/>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="18">
         <f>'④費用計算'!E12</f>
         <v/>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="18">
         <f>'④費用計算'!F12</f>
         <v/>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="18">
         <f>D7-C7</f>
         <v/>
       </c>
@@ -3354,19 +3398,19 @@
           <t>費用(円)</t>
         </is>
       </c>
-      <c r="B8" s="17">
+      <c r="B8" s="18">
         <f>'④費用計算'!C14</f>
         <v/>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="18">
         <f>'④費用計算'!H14</f>
         <v/>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="18">
         <f>'④費用計算'!I14</f>
         <v/>
       </c>
-      <c r="E8" s="17">
+      <c r="E8" s="18">
         <f>D8-C8</f>
         <v/>
       </c>
@@ -3377,18 +3421,18 @@
           <t>現状からの追加費用(円)</t>
         </is>
       </c>
-      <c r="B9" s="17" t="n">
+      <c r="B9" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="18">
         <f>C8-$B$8</f>
         <v/>
       </c>
-      <c r="D9" s="17">
+      <c r="D9" s="18">
         <f>D8-$B$8</f>
         <v/>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="18">
         <f>D9-C9</f>
         <v/>
       </c>
@@ -3399,19 +3443,19 @@
           <t>潜在患者カバー数(人)</t>
         </is>
       </c>
-      <c r="B10" s="17">
-        <f>SUMPRODUCT(('入力'!$F$20:$F$25&gt;0)*'入力'!$C$20:$C$25)</f>
-        <v/>
-      </c>
-      <c r="C10" s="17">
-        <f>SUMPRODUCT(('入力'!$G$20:$G$25&gt;0)*'入力'!$C$20:$C$25)</f>
-        <v/>
-      </c>
-      <c r="D10" s="17">
-        <f>SUMPRODUCT(('入力'!$H$20:$H$25&gt;0)*'入力'!$C$20:$C$25)</f>
-        <v/>
-      </c>
-      <c r="E10" s="17">
+      <c r="B10" s="18">
+        <f>SUMPRODUCT(('入力'!$F$21:$F$26&gt;0)*'入力'!$C$21:$C$26)</f>
+        <v/>
+      </c>
+      <c r="C10" s="18">
+        <f>SUMPRODUCT(('入力'!$G$21:$G$26&gt;0)*'入力'!$C$21:$C$26)</f>
+        <v/>
+      </c>
+      <c r="D10" s="18">
+        <f>SUMPRODUCT(('入力'!$H$21:$H$26&gt;0)*'入力'!$C$21:$C$26)</f>
+        <v/>
+      </c>
+      <c r="E10" s="18">
         <f>D10-C10</f>
         <v/>
       </c>
@@ -3422,18 +3466,18 @@
           <t>追加処方患者_保守(人)</t>
         </is>
       </c>
-      <c r="B11" s="20" t="n">
+      <c r="B11" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="20">
+      <c r="C11" s="21">
         <f>'⑤売上試算'!H11</f>
         <v/>
       </c>
-      <c r="D11" s="20">
+      <c r="D11" s="21">
         <f>'⑤売上試算'!K11</f>
         <v/>
       </c>
-      <c r="E11" s="20">
+      <c r="E11" s="21">
         <f>D11-C11</f>
         <v/>
       </c>
@@ -3444,18 +3488,18 @@
           <t>追加処方患者_基準(人)</t>
         </is>
       </c>
-      <c r="B12" s="20" t="n">
+      <c r="B12" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="C12" s="20">
+      <c r="C12" s="21">
         <f>'⑤売上試算'!I11</f>
         <v/>
       </c>
-      <c r="D12" s="20">
+      <c r="D12" s="21">
         <f>'⑤売上試算'!L11</f>
         <v/>
       </c>
-      <c r="E12" s="20">
+      <c r="E12" s="21">
         <f>D12-C12</f>
         <v/>
       </c>
@@ -3466,387 +3510,597 @@
           <t>追加処方患者_楽観(人)</t>
         </is>
       </c>
-      <c r="B13" s="20" t="n">
+      <c r="B13" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="C13" s="20">
+      <c r="C13" s="21">
         <f>'⑤売上試算'!J11</f>
         <v/>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="21">
         <f>'⑤売上試算'!M11</f>
         <v/>
       </c>
-      <c r="E13" s="20">
+      <c r="E13" s="21">
         <f>D13-C13</f>
         <v/>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>追加売上_保守(円)</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="17">
-        <f>'⑤売上試算'!H12</f>
-        <v/>
-      </c>
-      <c r="D14" s="17">
-        <f>'⑤売上試算'!K12</f>
-        <v/>
-      </c>
-      <c r="E14" s="17">
-        <f>D14-C14</f>
-        <v/>
-      </c>
-    </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>追加売上_基準(円)</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="17">
-        <f>'⑤売上試算'!I12</f>
-        <v/>
-      </c>
-      <c r="D15" s="17">
-        <f>'⑤売上試算'!L12</f>
-        <v/>
-      </c>
-      <c r="E15" s="17">
-        <f>D15-C15</f>
-        <v/>
+      <c r="A15" s="22" t="inlineStr">
+        <is>
+          <t>全国換算(市場全体31万人 = 回答医師の結果 × 全国換算の倍率)</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>追加売上_楽観(円)</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="n">
+          <t>配信対象医師数(全国、名)</t>
+        </is>
+      </c>
+      <c r="B16" s="18">
+        <f>B5*scale</f>
+        <v/>
+      </c>
+      <c r="C16" s="18">
+        <f>C5*scale</f>
+        <v/>
+      </c>
+      <c r="D16" s="18">
+        <f>D5*scale</f>
+        <v/>
+      </c>
+      <c r="E16" s="18">
+        <f>D16-C16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>費用(全国、円)</t>
+        </is>
+      </c>
+      <c r="B17" s="18">
+        <f>B8*scale</f>
+        <v/>
+      </c>
+      <c r="C17" s="18">
+        <f>C8*scale</f>
+        <v/>
+      </c>
+      <c r="D17" s="18">
+        <f>D8*scale</f>
+        <v/>
+      </c>
+      <c r="E17" s="18">
+        <f>D17-C17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>現状からの追加費用(全国、円)</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="C16" s="17">
-        <f>'⑤売上試算'!J12</f>
-        <v/>
-      </c>
-      <c r="D16" s="17">
-        <f>'⑤売上試算'!M12</f>
-        <v/>
-      </c>
-      <c r="E16" s="17">
-        <f>D16-C16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="18" t="inlineStr">
-        <is>
-          <t>費用対効果(追加売上_基準 ÷ 追加費用)</t>
-        </is>
-      </c>
-      <c r="C17" s="25">
-        <f>IF(C9&lt;=0,"追加費用なし",C15/C9)</f>
-        <v/>
-      </c>
-      <c r="D17" s="25">
-        <f>IF(D9&lt;=0,"追加費用なし",D15/D9)</f>
-        <v/>
-      </c>
-      <c r="E17" s="25">
-        <f>IF(E9&lt;=0,"",E15/E9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="18" t="inlineStr">
-        <is>
-          <t>費用回収に必要な利益率_保守(追加費用÷追加売上)</t>
-        </is>
-      </c>
-      <c r="C18" s="23">
-        <f>IF(C9&lt;=0,"不要",C9/C14)</f>
-        <v/>
-      </c>
-      <c r="D18" s="23">
-        <f>IF(D9&lt;=0,"不要",D9/D14)</f>
-        <v/>
-      </c>
-      <c r="E18" s="23">
-        <f>IF(E9&lt;=0,"",E9/E14)</f>
+      <c r="C18" s="18">
+        <f>C9*scale</f>
+        <v/>
+      </c>
+      <c r="D18" s="18">
+        <f>D9*scale</f>
+        <v/>
+      </c>
+      <c r="E18" s="18">
+        <f>D18-C18</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="inlineStr">
-        <is>
-          <t>費用回収に必要な利益率_基準</t>
-        </is>
-      </c>
-      <c r="C19" s="23">
-        <f>IF(C9&lt;=0,"不要",C9/C15)</f>
-        <v/>
-      </c>
-      <c r="D19" s="23">
-        <f>IF(D9&lt;=0,"不要",D9/D15)</f>
-        <v/>
-      </c>
-      <c r="E19" s="23">
-        <f>IF(E9&lt;=0,"",E9/E15)</f>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>追加処方患者_保守(全国、人)</t>
+        </is>
+      </c>
+      <c r="B19" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="18">
+        <f>C11*scale</f>
+        <v/>
+      </c>
+      <c r="D19" s="18">
+        <f>D11*scale</f>
+        <v/>
+      </c>
+      <c r="E19" s="18">
+        <f>D19-C19</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="inlineStr">
-        <is>
-          <t>予算判定(A案)</t>
-        </is>
-      </c>
-      <c r="C20" s="4">
-        <f>IF(C8&lt;=B8,"予算内","予算超過")</f>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>追加処方患者_基準(全国、人)</t>
+        </is>
+      </c>
+      <c r="B20" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="18">
+        <f>C12*scale</f>
+        <v/>
+      </c>
+      <c r="D20" s="18">
+        <f>D12*scale</f>
+        <v/>
+      </c>
+      <c r="E20" s="18">
+        <f>D20-C20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>追加処方患者_楽観(全国、人)</t>
+        </is>
+      </c>
+      <c r="B21" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="18">
+        <f>C13*scale</f>
+        <v/>
+      </c>
+      <c r="D21" s="18">
+        <f>D13*scale</f>
+        <v/>
+      </c>
+      <c r="E21" s="18">
+        <f>D21-C21</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="26" t="inlineStr">
-        <is>
-          <t>表示用(PPTと同じ丸め)</t>
-        </is>
-      </c>
-      <c r="B22" s="26" t="inlineStr">
-        <is>
-          <t>現状</t>
-        </is>
-      </c>
-      <c r="C22" s="26" t="inlineStr">
-        <is>
-          <t>A案</t>
-        </is>
-      </c>
-      <c r="D22" s="26" t="inlineStr">
-        <is>
-          <t>B案</t>
-        </is>
-      </c>
-      <c r="E22" s="26" t="inlineStr">
-        <is>
-          <t>B案 − A案</t>
-        </is>
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>追加売上_保守(全国、円)</t>
+        </is>
+      </c>
+      <c r="B22" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="18">
+        <f>C19*sales_per_pt</f>
+        <v/>
+      </c>
+      <c r="D22" s="18">
+        <f>D19*sales_per_pt</f>
+        <v/>
+      </c>
+      <c r="E22" s="18">
+        <f>D22-C22</f>
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>費用(万円、小数1桁)</t>
-        </is>
-      </c>
-      <c r="B23" s="4">
-        <f>ROUND(B8/10000,1)</f>
-        <v/>
-      </c>
-      <c r="C23" s="4">
-        <f>ROUND(C8/10000,1)</f>
-        <v/>
-      </c>
-      <c r="D23" s="4">
-        <f>ROUND(D8/10000,1)</f>
-        <v/>
-      </c>
-      <c r="E23" s="4">
-        <f>ROUND(D8/10000,1)-ROUND(C8/10000,1)</f>
+          <t>追加売上_基準(全国、円)</t>
+        </is>
+      </c>
+      <c r="B23" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="18">
+        <f>C20*sales_per_pt</f>
+        <v/>
+      </c>
+      <c r="D23" s="18">
+        <f>D20*sales_per_pt</f>
+        <v/>
+      </c>
+      <c r="E23" s="18">
+        <f>D23-C23</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>追加費用(万円、小数1桁)</t>
-        </is>
-      </c>
-      <c r="B24" s="4">
-        <f>ROUND(B9/10000,1)</f>
-        <v/>
-      </c>
-      <c r="C24" s="4">
-        <f>ROUND(C9/10000,1)</f>
-        <v/>
-      </c>
-      <c r="D24" s="4">
-        <f>ROUND(D9/10000,1)</f>
-        <v/>
-      </c>
-      <c r="E24" s="4">
-        <f>ROUND(D9/10000,1)-ROUND(C9/10000,1)</f>
+          <t>追加売上_楽観(全国、円)</t>
+        </is>
+      </c>
+      <c r="B24" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="18">
+        <f>C21*sales_per_pt</f>
+        <v/>
+      </c>
+      <c r="D24" s="18">
+        <f>D21*sales_per_pt</f>
+        <v/>
+      </c>
+      <c r="E24" s="18">
+        <f>D24-C24</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>既読件数</t>
-        </is>
-      </c>
-      <c r="B25" s="4">
-        <f>ROUND(B7,0)</f>
-        <v/>
-      </c>
-      <c r="C25" s="4">
-        <f>ROUND(C7,0)</f>
-        <v/>
-      </c>
-      <c r="D25" s="4">
-        <f>ROUND(D7,0)</f>
-        <v/>
-      </c>
-      <c r="E25" s="4">
-        <f>ROUND(D7,0)-ROUND(C7,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>追加処方患者_保守</t>
-        </is>
-      </c>
-      <c r="B26" s="4">
-        <f>ROUND(B11,0)</f>
-        <v/>
-      </c>
-      <c r="C26" s="4">
-        <f>ROUND(C11,0)</f>
-        <v/>
-      </c>
-      <c r="D26" s="4">
-        <f>ROUND(D11,0)</f>
-        <v/>
-      </c>
-      <c r="E26" s="4">
-        <f>ROUND(E11,0)</f>
+          <t>売上50億円に対する割合_基準</t>
+        </is>
+      </c>
+      <c r="B25" s="26">
+        <f>B23/sales_total</f>
+        <v/>
+      </c>
+      <c r="C25" s="26">
+        <f>C23/sales_total</f>
+        <v/>
+      </c>
+      <c r="D25" s="26">
+        <f>D23/sales_total</f>
+        <v/>
+      </c>
+      <c r="E25" s="26">
+        <f>D25-C25</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>追加処方患者_基準</t>
-        </is>
-      </c>
-      <c r="B27" s="4">
-        <f>ROUND(B12,0)</f>
-        <v/>
-      </c>
-      <c r="C27" s="4">
-        <f>ROUND(C12,0)</f>
-        <v/>
-      </c>
-      <c r="D27" s="4">
-        <f>ROUND(D12,0)</f>
-        <v/>
-      </c>
-      <c r="E27" s="4">
-        <f>ROUND(E12,0)</f>
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>費用回収に必要な利益率_保守(追加費用 ÷ 追加売上、全国)</t>
+        </is>
+      </c>
+      <c r="C27" s="24">
+        <f>IF(C18&lt;=0,"不要",C18/C22)</f>
+        <v/>
+      </c>
+      <c r="D27" s="24">
+        <f>IF(D18&lt;=0,"不要",D18/D22)</f>
+        <v/>
+      </c>
+      <c r="E27" s="24">
+        <f>IF(E18&lt;=0,"",E18/E22)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>追加処方患者_楽観</t>
-        </is>
-      </c>
-      <c r="B28" s="4">
-        <f>ROUND(B13,0)</f>
-        <v/>
-      </c>
-      <c r="C28" s="4">
-        <f>ROUND(C13,0)</f>
-        <v/>
-      </c>
-      <c r="D28" s="4">
-        <f>ROUND(D13,0)</f>
-        <v/>
-      </c>
-      <c r="E28" s="4">
-        <f>ROUND(E13,0)</f>
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>費用回収に必要な利益率_基準</t>
+        </is>
+      </c>
+      <c r="C28" s="24">
+        <f>IF(C18&lt;=0,"不要",C18/C23)</f>
+        <v/>
+      </c>
+      <c r="D28" s="24">
+        <f>IF(D18&lt;=0,"不要",D18/D23)</f>
+        <v/>
+      </c>
+      <c r="E28" s="24">
+        <f>IF(E18&lt;=0,"",E18/E23)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>追加売上_保守(万円)</t>
-        </is>
-      </c>
-      <c r="B29" s="4">
-        <f>ROUND(B14/10000,0)</f>
-        <v/>
-      </c>
-      <c r="C29" s="4">
-        <f>ROUND(C14/10000,0)</f>
-        <v/>
-      </c>
-      <c r="D29" s="4">
-        <f>ROUND(D14/10000,0)</f>
-        <v/>
-      </c>
-      <c r="E29" s="4">
-        <f>ROUND(D14/10000,0)-ROUND(C14/10000,0)</f>
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>費用回収に必要な利益率_楽観</t>
+        </is>
+      </c>
+      <c r="C29" s="24">
+        <f>IF(C18&lt;=0,"不要",C18/C24)</f>
+        <v/>
+      </c>
+      <c r="D29" s="24">
+        <f>IF(D18&lt;=0,"不要",D18/D24)</f>
+        <v/>
+      </c>
+      <c r="E29" s="24">
+        <f>IF(E18&lt;=0,"",E18/E24)</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>追加売上_基準(万円)</t>
-        </is>
-      </c>
-      <c r="B30" s="4">
-        <f>ROUND(B15/10000,0)</f>
-        <v/>
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>予算判定(A案)</t>
+        </is>
       </c>
       <c r="C30" s="4">
-        <f>ROUND(C15/10000,0)</f>
-        <v/>
-      </c>
-      <c r="D30" s="4">
-        <f>ROUND(D15/10000,0)</f>
-        <v/>
-      </c>
-      <c r="E30" s="4">
-        <f>ROUND(D15/10000,0)-ROUND(C15/10000,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>追加売上_楽観(万円)</t>
-        </is>
-      </c>
-      <c r="B31" s="4">
-        <f>ROUND(B16/10000,0)</f>
-        <v/>
-      </c>
-      <c r="C31" s="4">
-        <f>ROUND(C16/10000,0)</f>
-        <v/>
-      </c>
-      <c r="D31" s="4">
-        <f>ROUND(D16/10000,0)</f>
-        <v/>
-      </c>
-      <c r="E31" s="4">
-        <f>ROUND(D16/10000,0)-ROUND(C16/10000,0)</f>
+        <f>IF(C8&lt;=B8,"予算内","予算超過")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="27" t="inlineStr">
+        <is>
+          <t>表示用(PPTと同じ丸め)</t>
+        </is>
+      </c>
+      <c r="B32" s="27" t="inlineStr">
+        <is>
+          <t>現状</t>
+        </is>
+      </c>
+      <c r="C32" s="27" t="inlineStr">
+        <is>
+          <t>A案</t>
+        </is>
+      </c>
+      <c r="D32" s="27" t="inlineStr">
+        <is>
+          <t>B案</t>
+        </is>
+      </c>
+      <c r="E32" s="27" t="inlineStr">
+        <is>
+          <t>B案 − A案</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>費用(回答医師、万円、小数1桁)</t>
+        </is>
+      </c>
+      <c r="B33" s="4">
+        <f>ROUND(B8/10000,1)</f>
+        <v/>
+      </c>
+      <c r="C33" s="4">
+        <f>ROUND(C8/10000,1)</f>
+        <v/>
+      </c>
+      <c r="D33" s="4">
+        <f>ROUND(D8/10000,1)</f>
+        <v/>
+      </c>
+      <c r="E33" s="4">
+        <f>ROUND(D8/10000,1)-ROUND(C8/10000,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>費用(全国、万円)</t>
+        </is>
+      </c>
+      <c r="B34" s="4">
+        <f>ROUND(B17/10000,0)</f>
+        <v/>
+      </c>
+      <c r="C34" s="4">
+        <f>ROUND(C17/10000,0)</f>
+        <v/>
+      </c>
+      <c r="D34" s="4">
+        <f>ROUND(D17/10000,0)</f>
+        <v/>
+      </c>
+      <c r="E34" s="4">
+        <f>ROUND(D17/10000,0)-ROUND(C17/10000,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>追加費用(全国、万円)</t>
+        </is>
+      </c>
+      <c r="B35" s="4">
+        <f>ROUND(B18/10000,0)</f>
+        <v/>
+      </c>
+      <c r="C35" s="4">
+        <f>ROUND(C18/10000,0)</f>
+        <v/>
+      </c>
+      <c r="D35" s="4">
+        <f>ROUND(D18/10000,0)</f>
+        <v/>
+      </c>
+      <c r="E35" s="4">
+        <f>ROUND(D17/10000,0)-ROUND(C17/10000,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>配信対象医師数(全国、千人)</t>
+        </is>
+      </c>
+      <c r="B36" s="4">
+        <f>ROUND(B16/1000,1)</f>
+        <v/>
+      </c>
+      <c r="C36" s="4">
+        <f>ROUND(C16/1000,1)</f>
+        <v/>
+      </c>
+      <c r="D36" s="4">
+        <f>ROUND(D16/1000,1)</f>
+        <v/>
+      </c>
+      <c r="E36" s="4">
+        <f>ROUND(D16/1000,1)-ROUND(C16/1000,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>追加処方患者_保守(全国)</t>
+        </is>
+      </c>
+      <c r="B37" s="4">
+        <f>ROUND(B19,0)</f>
+        <v/>
+      </c>
+      <c r="C37" s="4">
+        <f>ROUND(C19,0)</f>
+        <v/>
+      </c>
+      <c r="D37" s="4">
+        <f>ROUND(D19,0)</f>
+        <v/>
+      </c>
+      <c r="E37" s="4">
+        <f>ROUND(D19,0)-ROUND(C19,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>追加処方患者_基準(全国)</t>
+        </is>
+      </c>
+      <c r="B38" s="4">
+        <f>ROUND(B20,0)</f>
+        <v/>
+      </c>
+      <c r="C38" s="4">
+        <f>ROUND(C20,0)</f>
+        <v/>
+      </c>
+      <c r="D38" s="4">
+        <f>ROUND(D20,0)</f>
+        <v/>
+      </c>
+      <c r="E38" s="4">
+        <f>ROUND(D20,0)-ROUND(C20,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>追加処方患者_楽観(全国)</t>
+        </is>
+      </c>
+      <c r="B39" s="4">
+        <f>ROUND(B21,0)</f>
+        <v/>
+      </c>
+      <c r="C39" s="4">
+        <f>ROUND(C21,0)</f>
+        <v/>
+      </c>
+      <c r="D39" s="4">
+        <f>ROUND(D21,0)</f>
+        <v/>
+      </c>
+      <c r="E39" s="4">
+        <f>ROUND(D21,0)-ROUND(C21,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>追加売上_保守(全国、万円)</t>
+        </is>
+      </c>
+      <c r="B40" s="4">
+        <f>ROUND(B22/10000,0)</f>
+        <v/>
+      </c>
+      <c r="C40" s="4">
+        <f>ROUND(C22/10000,0)</f>
+        <v/>
+      </c>
+      <c r="D40" s="4">
+        <f>ROUND(D22/10000,0)</f>
+        <v/>
+      </c>
+      <c r="E40" s="4">
+        <f>ROUND(D22/10000,0)-ROUND(C22/10000,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>追加売上_基準(全国、万円)</t>
+        </is>
+      </c>
+      <c r="B41" s="4">
+        <f>ROUND(B23/10000,0)</f>
+        <v/>
+      </c>
+      <c r="C41" s="4">
+        <f>ROUND(C23/10000,0)</f>
+        <v/>
+      </c>
+      <c r="D41" s="4">
+        <f>ROUND(D23/10000,0)</f>
+        <v/>
+      </c>
+      <c r="E41" s="4">
+        <f>ROUND(D23/10000,0)-ROUND(C23/10000,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>追加売上_楽観(全国、万円)</t>
+        </is>
+      </c>
+      <c r="B42" s="4">
+        <f>ROUND(B24/10000,0)</f>
+        <v/>
+      </c>
+      <c r="C42" s="4">
+        <f>ROUND(C24/10000,0)</f>
+        <v/>
+      </c>
+      <c r="D42" s="4">
+        <f>ROUND(D24/10000,0)</f>
+        <v/>
+      </c>
+      <c r="E42" s="4">
+        <f>ROUND(D24/10000,0)-ROUND(C24/10000,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>売上に対する割合_基準(%、小数2桁)</t>
+        </is>
+      </c>
+      <c r="B43" s="4">
+        <f>ROUND(B25*100,2)</f>
+        <v/>
+      </c>
+      <c r="C43" s="4">
+        <f>ROUND(C25*100,2)</f>
+        <v/>
+      </c>
+      <c r="D43" s="4">
+        <f>ROUND(D25*100,2)</f>
+        <v/>
+      </c>
+      <c r="E43" s="4">
+        <f>ROUND(D25*100,2)-ROUND(C25*100,2)</f>
         <v/>
       </c>
     </row>
@@ -3861,7 +4115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A19"/>
+  <dimension ref="A1:A21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="180" customWidth="1" min="1" max="1"/>
@@ -3912,82 +4166,96 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>【仮定】処方患者1人あたり年間売上 = 50億円 ÷ 全医師の処方患者推計22,560人(回答医師11,280人×10,000/5,000)。全医師10,000名の処方が売上のすべてと仮定。実際の単価が分かれば①で上書き。</t>
+          <t>【全国換算】市場全体 = m3.com登録医師310,000人(国内医師の約90%、M3会社資料)。データの10,000名はその一部とみなし、回答医師5,000名の結果を62倍して全国に換算(回答医師が市場全体と同じ構成と仮定)。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>【仮定】既読医師率のモデル: 年f回配信時 = 1 −(1 − 10回時の既読医師率)^(f/10)。配信ごとの読まれやすさが一定と仮定。10回を超える分は未読の上位コンテンツの再配信。</t>
+          <t>【仮定】処方患者1人あたり年間売上 = 50億円 ÷ 全国の処方患者推計(回答医師11,280人 × 62) = 約7,149円。実際の単価が分かれば①で上書き。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>【仮定】①未接触の重点医師の既読率は、配信中・MR面談なしの重点医師(②)の実測値を使う。</t>
+          <t xml:space="preserve">  性質: 全国の追加売上 = 回答医師の追加処方患者 × 50億円 ÷ 回答医師の処方患者 となり、市場の医師数の前提に左右されない。全国の費用は医師数に比例する(B案の判断に影響する)。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>【補正】平均への回帰: MR面談・MR君の接点がない両年回答医師で、潜在8人以上だった医師の翌年の潜在は0.78倍、5〜7人は1.02倍、0〜2人は2.16倍(全診療科、M1)。翌年の潜在で効果を計算。</t>
+          <t>【仮定】既読医師率のモデル: 年f回配信時 = 1 −(1 − 10回時の既読医師率)^(f/10)。配信ごとの読まれやすさが一定と仮定。10回を超える分は未読の上位コンテンツの再配信。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>【仮定】増分転換率(保守1%・基準3%・楽観6%): 既読した医師の潜在未処方のうち、配信によって新たに処方される割合。配信を減らす③で失う効果も同じ値で差し引く。</t>
+          <t>【仮定】①未接触の重点医師の既読率は、配信中・MR面談なしの重点医師(②)の実測値を使う。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  参考値(観察、因果ではない): MR面談のない両年回答2,945名で、配信対象は対象外より処方率の伸びが2.3pt大きかった(95%区間1.1〜3.5pt)。既読医師1人・潜在あたりに換算すると約6.0%(下限2.8%)。楽観=中央、基準=下限、保守=約3分の1。</t>
+          <t>【補正】平均への回帰: MR面談・MR君の接点がない両年回答医師で、潜在8人以上だった医師の翌年の潜在は0.78倍、5〜7人は1.02倍、0〜2人は2.16倍(全診療科、M1)。翌年の潜在で効果を計算。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>【予測に幅がある理由】①増分転換率(観察データのみ) ②再配信時の既読率(未検証) ③1人あたり売上(単価・処方日数が不明) ④自己申告の患者数(年ごとに変動)。</t>
+          <t>【仮定】増分転換率(保守1%・基準3%・楽観6%): 既読した医師の潜在未処方のうち、配信によって新たに処方される割合。配信を減らす③で失う効果も同じ値で差し引く。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>【含めないもの】施策②(配信順)による既読率の上乗せ(KPIで確認)、④MR面談がある重点医師の変化(現状維持)、施策をしなくても起きる処方の変化。</t>
+          <t xml:space="preserve">  参考値(観察、因果ではない): MR面談のない両年回答2,945名で、配信対象は対象外より処方率の伸びが2.3pt大きかった(95%区間1.1〜3.5pt)。既読医師1人・潜在あたりに換算すると約6.0%(下限2.8%)。楽観=中央、基準=下限、保守=約3分の1。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>【売上と利益】追加売上は売上であり利益ではない。費用との比較は「費用回収に必要な利益率」で示す。</t>
+          <t>【予測に幅がある理由】①増分転換率(観察データのみ) ②再配信時の既読率(未検証) ③全国換算(回答医師が市場全体と同じ構成という仮定) ④自己申告の患者数(年ごとに変動)。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>【未確認の実施条件】新規配信先の配信資格・同意・配信停止、MR君で医師別・診療科別に配信順・回数を指定できるか、コンテンツ本文の内容確認、制作費・運用費。</t>
+          <t>【含めないもの】施策②(配信順)による既読率の上乗せ(KPIで確認)、④MR面談がある重点医師の変化(現状維持)、施策をしなくても起きる処方の変化。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>【対象範囲】回答医師5,000名のみ(非回答の5,000名は患者数が分からないため含めない)。1年間の試算で、2027年の予測ではない。</t>
+          <t>【売上と利益】追加売上は売上であり利益ではない。費用との比較は「費用回収に必要な利益率」(全国の追加費用 ÷ 全国の追加売上)で示す。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>【未確認の実施条件】新規配信先の配信資格・同意・配信停止、MR君で医師別・診療科別に配信順・回数を指定できるか、コンテンツ本文の内容確認、制作費・運用費。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>【対象範囲】試算の基礎は回答医師5,000名(潜在患者数が分かる医師)。全国換算は、同じルールを市場全体に当てはめた場合(全国展開には、アンケート等で潜在患者数を把握する必要がある)。1年間の試算で、2027年の予測ではない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>【使わない分析】完読・コンテンツ別の処方効果・動画の長さの分析、医師の重視割合とコンテンツ本数の割合の比較、v3・v4の試算値は使用していない。</t>
         </is>
